--- a/research/traditional_assets/database/data/tanzania/tanzania_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/tanzania/tanzania_telecom_wireless.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1115902789661804</v>
+        <v>0.1112870081292818</v>
       </c>
       <c r="C2">
-        <v>866.0618135723452</v>
+        <v>861.2234428662965</v>
       </c>
       <c r="D2">
-        <v>799.9618135723451</v>
+        <v>803.6664428662965</v>
       </c>
       <c r="E2">
-        <v>-136.8</v>
+        <v>-128.257</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.542999999999999</v>
       </c>
       <c r="G2">
         <v>66.09999999999999</v>
@@ -1451,28 +1451,28 @@
         <v>98.05</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4297129</v>
       </c>
       <c r="N2">
-        <v>98.05</v>
+        <v>97.6202871</v>
       </c>
       <c r="O2">
-        <v>29.415</v>
+        <v>29.28608613</v>
       </c>
       <c r="P2">
-        <v>68.63499999999999</v>
+        <v>68.33420097</v>
       </c>
       <c r="Q2">
-        <v>167.835</v>
+        <v>167.53420097</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1115902789661804</v>
+        <v>0.1120554627568503</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549506</v>
+        <v>0.6407409627425109</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>228.1756028269107</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1112870081292818</v>
+        <v>0.1109837372923833</v>
       </c>
       <c r="C3">
-        <v>861.2234428662965</v>
+        <v>856.4195441335664</v>
       </c>
       <c r="D3">
-        <v>803.6664428662965</v>
+        <v>807.4055441335664</v>
       </c>
       <c r="E3">
-        <v>-128.257</v>
+        <v>-119.714</v>
       </c>
       <c r="F3">
-        <v>8.542999999999999</v>
+        <v>17.086</v>
       </c>
       <c r="G3">
         <v>66.09999999999999</v>
@@ -1533,28 +1533,28 @@
         <v>98.05</v>
       </c>
       <c r="M3">
-        <v>0.4297129</v>
+        <v>0.8594257999999999</v>
       </c>
       <c r="N3">
-        <v>97.6202871</v>
+        <v>97.1905742</v>
       </c>
       <c r="O3">
-        <v>29.28608613</v>
+        <v>29.15717226</v>
       </c>
       <c r="P3">
-        <v>68.33420097</v>
+        <v>68.03340194</v>
       </c>
       <c r="Q3">
-        <v>167.53420097</v>
+        <v>167.23340194</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1120554627568503</v>
+        <v>0.1125301400942686</v>
       </c>
       <c r="T3">
-        <v>0.6407409627425109</v>
+        <v>0.6453314553828785</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>228.1756028269107</v>
+        <v>114.0878014134554</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1109837372923833</v>
+        <v>0.1106804664554847</v>
       </c>
       <c r="C4">
-        <v>856.4195441335664</v>
+        <v>851.650600771305</v>
       </c>
       <c r="D4">
-        <v>807.4055441335664</v>
+        <v>811.179600771305</v>
       </c>
       <c r="E4">
-        <v>-119.714</v>
+        <v>-111.171</v>
       </c>
       <c r="F4">
-        <v>17.086</v>
+        <v>25.629</v>
       </c>
       <c r="G4">
         <v>66.09999999999999</v>
@@ -1615,28 +1615,28 @@
         <v>98.05</v>
       </c>
       <c r="M4">
-        <v>0.8594257999999999</v>
+        <v>1.2891387</v>
       </c>
       <c r="N4">
-        <v>97.1905742</v>
+        <v>96.7608613</v>
       </c>
       <c r="O4">
-        <v>29.15717226</v>
+        <v>29.02825839</v>
       </c>
       <c r="P4">
-        <v>68.03340194</v>
+        <v>67.73260291</v>
       </c>
       <c r="Q4">
-        <v>167.23340194</v>
+        <v>166.93260291</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1125301400942686</v>
+        <v>0.1130146045932832</v>
       </c>
       <c r="T4">
-        <v>0.6453314553828785</v>
+        <v>0.6500165973560371</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>114.0878014134554</v>
+        <v>76.05853427563692</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1106804664554847</v>
+        <v>0.1103771956185862</v>
       </c>
       <c r="C5">
-        <v>851.650600771305</v>
+        <v>846.9171052572838</v>
       </c>
       <c r="D5">
-        <v>811.179600771305</v>
+        <v>814.9891052572838</v>
       </c>
       <c r="E5">
-        <v>-111.171</v>
+        <v>-102.628</v>
       </c>
       <c r="F5">
-        <v>25.629</v>
+        <v>34.172</v>
       </c>
       <c r="G5">
         <v>66.09999999999999</v>
@@ -1697,28 +1697,28 @@
         <v>98.05</v>
       </c>
       <c r="M5">
-        <v>1.2891387</v>
+        <v>1.7188516</v>
       </c>
       <c r="N5">
-        <v>96.7608613</v>
+        <v>96.3311484</v>
       </c>
       <c r="O5">
-        <v>29.02825839</v>
+        <v>28.89934452</v>
       </c>
       <c r="P5">
-        <v>67.73260291</v>
+        <v>67.43180388</v>
       </c>
       <c r="Q5">
-        <v>166.93260291</v>
+        <v>166.63180388</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1130146045932832</v>
+        <v>0.113509162102694</v>
       </c>
       <c r="T5">
-        <v>0.6500165973560371</v>
+        <v>0.6547993464536367</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>76.05853427563692</v>
+        <v>57.04390070672768</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1103771956185862</v>
+        <v>0.1100739247816876</v>
       </c>
       <c r="C6">
-        <v>846.9171052572838</v>
+        <v>842.2195593641255</v>
       </c>
       <c r="D6">
-        <v>814.9891052572838</v>
+        <v>818.8345593641255</v>
       </c>
       <c r="E6">
-        <v>-102.628</v>
+        <v>-94.08500000000001</v>
       </c>
       <c r="F6">
-        <v>34.172</v>
+        <v>42.715</v>
       </c>
       <c r="G6">
         <v>66.09999999999999</v>
@@ -1779,28 +1779,28 @@
         <v>98.05</v>
       </c>
       <c r="M6">
-        <v>1.7188516</v>
+        <v>2.1485645</v>
       </c>
       <c r="N6">
-        <v>96.3311484</v>
+        <v>95.90143549999999</v>
       </c>
       <c r="O6">
-        <v>28.89934452</v>
+        <v>28.77043065</v>
       </c>
       <c r="P6">
-        <v>67.43180388</v>
+        <v>67.13100485</v>
       </c>
       <c r="Q6">
-        <v>166.63180388</v>
+        <v>166.33100485</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.113509162102694</v>
+        <v>0.1140141313491449</v>
       </c>
       <c r="T6">
-        <v>0.6547993464536367</v>
+        <v>0.6596827850059225</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>57.04390070672768</v>
+        <v>45.63512056538214</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1100739247816876</v>
+        <v>0.1097706539447891</v>
       </c>
       <c r="C7">
-        <v>842.2195593641255</v>
+        <v>837.5584743796284</v>
       </c>
       <c r="D7">
-        <v>818.8345593641255</v>
+        <v>822.7164743796284</v>
       </c>
       <c r="E7">
-        <v>-94.08500000000001</v>
+        <v>-85.542</v>
       </c>
       <c r="F7">
-        <v>42.715</v>
+        <v>51.258</v>
       </c>
       <c r="G7">
         <v>66.09999999999999</v>
@@ -1861,28 +1861,28 @@
         <v>98.05</v>
       </c>
       <c r="M7">
-        <v>2.1485645</v>
+        <v>2.5782774</v>
       </c>
       <c r="N7">
-        <v>95.90143549999999</v>
+        <v>95.47172259999999</v>
       </c>
       <c r="O7">
-        <v>28.77043065</v>
+        <v>28.64151678</v>
       </c>
       <c r="P7">
-        <v>67.13100485</v>
+        <v>66.83020582</v>
       </c>
       <c r="Q7">
-        <v>166.33100485</v>
+        <v>166.03020582</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1140141313491449</v>
+        <v>0.1145298446221161</v>
       </c>
       <c r="T7">
-        <v>0.6596827850059225</v>
+        <v>0.6646701265061292</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.63512056538214</v>
+        <v>38.02926713781844</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1097706539447891</v>
+        <v>0.1094673831078906</v>
       </c>
       <c r="C8">
-        <v>837.5584743796284</v>
+        <v>832.9343713333872</v>
       </c>
       <c r="D8">
-        <v>822.7164743796284</v>
+        <v>826.6353713333872</v>
       </c>
       <c r="E8">
-        <v>-85.54200000000002</v>
+        <v>-76.99900000000002</v>
       </c>
       <c r="F8">
-        <v>51.258</v>
+        <v>59.80099999999999</v>
       </c>
       <c r="G8">
         <v>66.09999999999999</v>
@@ -1943,28 +1943,28 @@
         <v>98.05</v>
       </c>
       <c r="M8">
-        <v>2.5782774</v>
+        <v>3.007990299999999</v>
       </c>
       <c r="N8">
-        <v>95.47172259999999</v>
+        <v>95.04200969999999</v>
       </c>
       <c r="O8">
-        <v>28.64151678</v>
+        <v>28.51260291</v>
       </c>
       <c r="P8">
-        <v>66.83020582</v>
+        <v>66.52940679</v>
       </c>
       <c r="Q8">
-        <v>166.03020582</v>
+        <v>165.72940679</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1145298446221161</v>
+        <v>0.1150566485031081</v>
       </c>
       <c r="T8">
-        <v>0.6646701265061292</v>
+        <v>0.6697647226622545</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>38.02926713781845</v>
+        <v>32.59651468955867</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1094673831078906</v>
+        <v>0.109164112270992</v>
       </c>
       <c r="C9">
-        <v>832.9343713333873</v>
+        <v>828.3477812299241</v>
       </c>
       <c r="D9">
-        <v>826.6353713333873</v>
+        <v>830.5917812299241</v>
       </c>
       <c r="E9">
-        <v>-76.99900000000001</v>
+        <v>-68.45600000000002</v>
       </c>
       <c r="F9">
-        <v>59.801</v>
+        <v>68.34399999999999</v>
       </c>
       <c r="G9">
         <v>66.09999999999999</v>
@@ -2025,28 +2025,28 @@
         <v>98.05</v>
       </c>
       <c r="M9">
-        <v>3.0079903</v>
+        <v>3.4377032</v>
       </c>
       <c r="N9">
-        <v>95.04200969999999</v>
+        <v>94.6122968</v>
       </c>
       <c r="O9">
-        <v>28.51260291</v>
+        <v>28.38368904</v>
       </c>
       <c r="P9">
-        <v>66.52940679</v>
+        <v>66.22860776</v>
       </c>
       <c r="Q9">
-        <v>165.72940679</v>
+        <v>165.42860776</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1150566485031081</v>
+        <v>0.1155949046423826</v>
       </c>
       <c r="T9">
-        <v>0.6697647226622545</v>
+        <v>0.6749700709087303</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.59651468955867</v>
+        <v>28.52195035336384</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.109164112270992</v>
+        <v>0.1088608414340935</v>
       </c>
       <c r="C10">
-        <v>828.3477812299241</v>
+        <v>823.7992452885411</v>
       </c>
       <c r="D10">
-        <v>830.5917812299241</v>
+        <v>834.586245288541</v>
       </c>
       <c r="E10">
-        <v>-68.45600000000002</v>
+        <v>-59.91300000000003</v>
       </c>
       <c r="F10">
-        <v>68.34399999999999</v>
+        <v>76.88699999999999</v>
       </c>
       <c r="G10">
         <v>66.09999999999999</v>
@@ -2107,28 +2107,28 @@
         <v>98.05</v>
       </c>
       <c r="M10">
-        <v>3.4377032</v>
+        <v>3.867416099999999</v>
       </c>
       <c r="N10">
-        <v>94.6122968</v>
+        <v>94.1825839</v>
       </c>
       <c r="O10">
-        <v>28.38368904</v>
+        <v>28.25477517</v>
       </c>
       <c r="P10">
-        <v>66.22860776</v>
+        <v>65.92780873</v>
       </c>
       <c r="Q10">
-        <v>165.42860776</v>
+        <v>165.12780873</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1155949046423826</v>
+        <v>0.1161449905869159</v>
       </c>
       <c r="T10">
-        <v>0.6749700709087303</v>
+        <v>0.6802898224133703</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.52195035336384</v>
+        <v>25.35284475854564</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1088608414340935</v>
+        <v>0.108557570597195</v>
       </c>
       <c r="C11">
-        <v>823.7992452885411</v>
+        <v>819.2893151901346</v>
       </c>
       <c r="D11">
-        <v>834.586245288541</v>
+        <v>838.6193151901346</v>
       </c>
       <c r="E11">
-        <v>-59.91300000000003</v>
+        <v>-51.37000000000002</v>
       </c>
       <c r="F11">
-        <v>76.88699999999999</v>
+        <v>85.42999999999999</v>
       </c>
       <c r="G11">
         <v>66.09999999999999</v>
@@ -2189,28 +2189,28 @@
         <v>98.05</v>
       </c>
       <c r="M11">
-        <v>3.867416099999999</v>
+        <v>4.297128999999999</v>
       </c>
       <c r="N11">
-        <v>94.1825839</v>
+        <v>93.752871</v>
       </c>
       <c r="O11">
-        <v>28.25477517</v>
+        <v>28.1258613</v>
       </c>
       <c r="P11">
-        <v>65.92780873</v>
+        <v>65.6270097</v>
       </c>
       <c r="Q11">
-        <v>165.12780873</v>
+        <v>164.8270097</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1161449905869159</v>
+        <v>0.11670730066355</v>
       </c>
       <c r="T11">
-        <v>0.6802898224133703</v>
+        <v>0.6857277906181134</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.35284475854564</v>
+        <v>22.81756028269108</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.108557570597195</v>
+        <v>0.1082542997602964</v>
       </c>
       <c r="C12">
-        <v>819.2893151901346</v>
+        <v>814.818553331193</v>
       </c>
       <c r="D12">
-        <v>838.6193151901346</v>
+        <v>842.6915533311929</v>
       </c>
       <c r="E12">
-        <v>-51.37</v>
+        <v>-42.82700000000001</v>
       </c>
       <c r="F12">
-        <v>85.43000000000001</v>
+        <v>93.973</v>
       </c>
       <c r="G12">
         <v>66.09999999999999</v>
@@ -2271,28 +2271,28 @@
         <v>98.05</v>
       </c>
       <c r="M12">
-        <v>4.297129</v>
+        <v>4.7268419</v>
       </c>
       <c r="N12">
-        <v>93.752871</v>
+        <v>93.3231581</v>
       </c>
       <c r="O12">
-        <v>28.1258613</v>
+        <v>27.99694743</v>
       </c>
       <c r="P12">
-        <v>65.6270097</v>
+        <v>65.32621066999999</v>
       </c>
       <c r="Q12">
-        <v>164.8270097</v>
+        <v>164.52621067</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.11670730066355</v>
+        <v>0.1172822469216814</v>
       </c>
       <c r="T12">
-        <v>0.6857277906181134</v>
+        <v>0.6912879603555475</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.81756028269107</v>
+        <v>20.74323662062825</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1082542997602964</v>
+        <v>0.1079510289233979</v>
       </c>
       <c r="C13">
-        <v>814.818553331193</v>
+        <v>810.3875330852384</v>
       </c>
       <c r="D13">
-        <v>842.6915533311929</v>
+        <v>846.8035330852383</v>
       </c>
       <c r="E13">
-        <v>-42.82700000000001</v>
+        <v>-34.28400000000002</v>
       </c>
       <c r="F13">
-        <v>93.973</v>
+        <v>102.516</v>
       </c>
       <c r="G13">
         <v>66.09999999999999</v>
@@ -2353,28 +2353,28 @@
         <v>98.05</v>
       </c>
       <c r="M13">
-        <v>4.7268419</v>
+        <v>5.156554799999999</v>
       </c>
       <c r="N13">
-        <v>93.3231581</v>
+        <v>92.8934452</v>
       </c>
       <c r="O13">
-        <v>27.99694743</v>
+        <v>27.86803356</v>
       </c>
       <c r="P13">
-        <v>65.32621066999999</v>
+        <v>65.02541164</v>
       </c>
       <c r="Q13">
-        <v>164.52621067</v>
+        <v>164.22541164</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1172822469216814</v>
+        <v>0.1178702601402249</v>
       </c>
       <c r="T13">
-        <v>0.6912879603555475</v>
+        <v>0.6969744975870141</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.74323662062825</v>
+        <v>19.01463356890923</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1079510289233979</v>
+        <v>0.1076477580864993</v>
       </c>
       <c r="C14">
-        <v>810.3875330852384</v>
+        <v>805.9968390719523</v>
       </c>
       <c r="D14">
-        <v>846.8035330852383</v>
+        <v>850.9558390719523</v>
       </c>
       <c r="E14">
-        <v>-34.28400000000002</v>
+        <v>-25.74100000000001</v>
       </c>
       <c r="F14">
-        <v>102.516</v>
+        <v>111.059</v>
       </c>
       <c r="G14">
         <v>66.09999999999999</v>
@@ -2435,28 +2435,28 @@
         <v>98.05</v>
       </c>
       <c r="M14">
-        <v>5.156554799999999</v>
+        <v>5.5862677</v>
       </c>
       <c r="N14">
-        <v>92.8934452</v>
+        <v>92.4637323</v>
       </c>
       <c r="O14">
-        <v>27.86803356</v>
+        <v>27.73911969</v>
       </c>
       <c r="P14">
-        <v>65.02541164</v>
+        <v>64.72461261000001</v>
       </c>
       <c r="Q14">
-        <v>164.22541164</v>
+        <v>163.92461261</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1178702601402249</v>
+        <v>0.1184717909040222</v>
       </c>
       <c r="T14">
-        <v>0.6969744975870141</v>
+        <v>0.7027917598123075</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.01463356890923</v>
+        <v>17.5519694482239</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1076477580864993</v>
+        <v>0.1073444872496008</v>
       </c>
       <c r="C15">
-        <v>805.9968390719523</v>
+        <v>801.6470674342655</v>
       </c>
       <c r="D15">
-        <v>850.9558390719523</v>
+        <v>855.1490674342655</v>
       </c>
       <c r="E15">
-        <v>-25.74100000000001</v>
+        <v>-17.19800000000001</v>
       </c>
       <c r="F15">
-        <v>111.059</v>
+        <v>119.602</v>
       </c>
       <c r="G15">
         <v>66.09999999999999</v>
@@ -2517,28 +2517,28 @@
         <v>98.05</v>
       </c>
       <c r="M15">
-        <v>5.5862677</v>
+        <v>6.0159806</v>
       </c>
       <c r="N15">
-        <v>92.4637323</v>
+        <v>92.03401939999999</v>
       </c>
       <c r="O15">
-        <v>27.73911969</v>
+        <v>27.61020582</v>
       </c>
       <c r="P15">
-        <v>64.72461261000001</v>
+        <v>64.42381358</v>
       </c>
       <c r="Q15">
-        <v>163.92461261</v>
+        <v>163.62381358</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1184717909040222</v>
+        <v>0.1190873107553498</v>
       </c>
       <c r="T15">
-        <v>0.7027917598123075</v>
+        <v>0.708744307205631</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.5519694482239</v>
+        <v>16.29825734477934</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1073444872496008</v>
+        <v>0.1070412164127022</v>
       </c>
       <c r="C16">
-        <v>801.6470674342655</v>
+        <v>797.3388261236768</v>
       </c>
       <c r="D16">
-        <v>855.1490674342655</v>
+        <v>859.3838261236767</v>
       </c>
       <c r="E16">
-        <v>-17.19800000000001</v>
+        <v>-8.655000000000001</v>
       </c>
       <c r="F16">
-        <v>119.602</v>
+        <v>128.145</v>
       </c>
       <c r="G16">
         <v>66.09999999999999</v>
@@ -2599,28 +2599,28 @@
         <v>98.05</v>
       </c>
       <c r="M16">
-        <v>6.0159806</v>
+        <v>6.4456935</v>
       </c>
       <c r="N16">
-        <v>92.03401939999999</v>
+        <v>91.60430649999999</v>
       </c>
       <c r="O16">
-        <v>27.61020582</v>
+        <v>27.48129195</v>
       </c>
       <c r="P16">
-        <v>64.42381358</v>
+        <v>64.12301454999999</v>
       </c>
       <c r="Q16">
-        <v>163.62381358</v>
+        <v>163.32301455</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1190873107553498</v>
+        <v>0.1197173134267085</v>
       </c>
       <c r="T16">
-        <v>0.708744307205631</v>
+        <v>0.714836914537621</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.29825734477934</v>
+        <v>15.21170685512738</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1070412164127022</v>
+        <v>0.1067379455758037</v>
       </c>
       <c r="C17">
-        <v>797.3388261236768</v>
+        <v>793.0727351940914</v>
       </c>
       <c r="D17">
-        <v>859.3838261236767</v>
+        <v>863.6607351940913</v>
       </c>
       <c r="E17">
-        <v>-8.65500000000003</v>
+        <v>-0.1120000000000232</v>
       </c>
       <c r="F17">
-        <v>128.145</v>
+        <v>136.688</v>
       </c>
       <c r="G17">
         <v>66.09999999999999</v>
@@ -2681,28 +2681,28 @@
         <v>98.05</v>
       </c>
       <c r="M17">
-        <v>6.445693499999999</v>
+        <v>6.875406399999999</v>
       </c>
       <c r="N17">
-        <v>91.60430649999999</v>
+        <v>91.17459359999999</v>
       </c>
       <c r="O17">
-        <v>27.48129195</v>
+        <v>27.35237808</v>
       </c>
       <c r="P17">
-        <v>64.12301454999999</v>
+        <v>63.82221552</v>
       </c>
       <c r="Q17">
-        <v>163.32301455</v>
+        <v>163.02221552</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1197173134267085</v>
+        <v>0.1203623161616711</v>
       </c>
       <c r="T17">
-        <v>0.714836914537621</v>
+        <v>0.7210745839489441</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.21170685512738</v>
+        <v>14.26097517668192</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1067379455758037</v>
+        <v>0.1064346747389052</v>
       </c>
       <c r="C18">
-        <v>793.0727351940914</v>
+        <v>788.8494271044805</v>
       </c>
       <c r="D18">
-        <v>863.6607351940913</v>
+        <v>867.9804271044804</v>
       </c>
       <c r="E18">
-        <v>-0.1120000000000232</v>
+        <v>8.430999999999983</v>
       </c>
       <c r="F18">
-        <v>136.688</v>
+        <v>145.231</v>
       </c>
       <c r="G18">
         <v>66.09999999999999</v>
@@ -2763,28 +2763,28 @@
         <v>98.05</v>
       </c>
       <c r="M18">
-        <v>6.875406399999999</v>
+        <v>7.305119299999999</v>
       </c>
       <c r="N18">
-        <v>91.17459359999999</v>
+        <v>90.7448807</v>
       </c>
       <c r="O18">
-        <v>27.35237808</v>
+        <v>27.22346421</v>
       </c>
       <c r="P18">
-        <v>63.82221552</v>
+        <v>63.52141648999999</v>
       </c>
       <c r="Q18">
-        <v>163.02221552</v>
+        <v>162.72141649</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1203623161616711</v>
+        <v>0.1210228611312111</v>
       </c>
       <c r="T18">
-        <v>0.7210745839489441</v>
+        <v>0.727462558647287</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.26097517668192</v>
+        <v>13.42209428393592</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1064346747389052</v>
+        <v>0.1063204039020066</v>
       </c>
       <c r="C19">
-        <v>788.8494271044805</v>
+        <v>781.9452933945564</v>
       </c>
       <c r="D19">
-        <v>867.9804271044804</v>
+        <v>869.6192933945564</v>
       </c>
       <c r="E19">
-        <v>8.430999999999983</v>
+        <v>16.97399999999999</v>
       </c>
       <c r="F19">
-        <v>145.231</v>
+        <v>153.774</v>
       </c>
       <c r="G19">
         <v>66.09999999999999</v>
@@ -2845,45 +2845,45 @@
         <v>98.05</v>
       </c>
       <c r="M19">
-        <v>7.305119299999999</v>
+        <v>7.9654932</v>
       </c>
       <c r="N19">
-        <v>90.7448807</v>
+        <v>90.0845068</v>
       </c>
       <c r="O19">
-        <v>27.22346421</v>
+        <v>27.02535204</v>
       </c>
       <c r="P19">
-        <v>63.52141648999999</v>
+        <v>63.05915476</v>
       </c>
       <c r="Q19">
-        <v>162.72141649</v>
+        <v>162.25915476</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1210228611312111</v>
+        <v>0.1216995169536666</v>
       </c>
       <c r="T19">
-        <v>0.727462558647287</v>
+        <v>0.734006337606565</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.42209428393592</v>
+        <v>12.30934451114716</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1063204039020066</v>
+        <v>0.1060276330651081</v>
       </c>
       <c r="C20">
-        <v>781.9452933945562</v>
+        <v>777.6295750483949</v>
       </c>
       <c r="D20">
-        <v>869.6192933945562</v>
+        <v>873.8465750483949</v>
       </c>
       <c r="E20">
-        <v>16.97399999999996</v>
+        <v>25.517</v>
       </c>
       <c r="F20">
-        <v>153.774</v>
+        <v>162.317</v>
       </c>
       <c r="G20">
         <v>66.09999999999999</v>
@@ -2927,28 +2927,28 @@
         <v>98.05</v>
       </c>
       <c r="M20">
-        <v>7.965493199999998</v>
+        <v>8.4080206</v>
       </c>
       <c r="N20">
-        <v>90.0845068</v>
+        <v>89.6419794</v>
       </c>
       <c r="O20">
-        <v>27.02535204</v>
+        <v>26.89259382</v>
       </c>
       <c r="P20">
-        <v>63.05915476</v>
+        <v>62.74938557999999</v>
       </c>
       <c r="Q20">
-        <v>162.25915476</v>
+        <v>161.94938558</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1216995169536666</v>
+        <v>0.1223928803272939</v>
       </c>
       <c r="T20">
-        <v>0.734006337606565</v>
+        <v>0.740711691354961</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.30934451114716</v>
+        <v>11.66148427371836</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1060276330651081</v>
+        <v>0.1057348622282095</v>
       </c>
       <c r="C21">
-        <v>777.6295750483949</v>
+        <v>773.3551556972283</v>
       </c>
       <c r="D21">
-        <v>873.8465750483949</v>
+        <v>878.1151556972283</v>
       </c>
       <c r="E21">
-        <v>25.517</v>
+        <v>34.06</v>
       </c>
       <c r="F21">
-        <v>162.317</v>
+        <v>170.86</v>
       </c>
       <c r="G21">
         <v>66.09999999999999</v>
@@ -3009,28 +3009,28 @@
         <v>98.05</v>
       </c>
       <c r="M21">
-        <v>8.4080206</v>
+        <v>8.850548</v>
       </c>
       <c r="N21">
-        <v>89.6419794</v>
+        <v>89.19945199999999</v>
       </c>
       <c r="O21">
-        <v>26.89259382</v>
+        <v>26.7598356</v>
       </c>
       <c r="P21">
-        <v>62.74938557999999</v>
+        <v>62.43961639999999</v>
       </c>
       <c r="Q21">
-        <v>161.94938558</v>
+        <v>161.6396164</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1223928803272939</v>
+        <v>0.1231035777852619</v>
       </c>
       <c r="T21">
-        <v>0.740711691354961</v>
+        <v>0.747584678947067</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.66148427371836</v>
+        <v>11.07841006003244</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1057348622282095</v>
+        <v>0.105442091391311</v>
       </c>
       <c r="C22">
-        <v>773.3551556972283</v>
+        <v>769.1226435260342</v>
       </c>
       <c r="D22">
-        <v>878.1151556972283</v>
+        <v>882.4256435260342</v>
       </c>
       <c r="E22">
-        <v>34.06</v>
+        <v>42.60300000000001</v>
       </c>
       <c r="F22">
-        <v>170.86</v>
+        <v>179.403</v>
       </c>
       <c r="G22">
         <v>66.09999999999999</v>
@@ -3091,28 +3091,28 @@
         <v>98.05</v>
       </c>
       <c r="M22">
-        <v>8.850548</v>
+        <v>9.293075400000001</v>
       </c>
       <c r="N22">
-        <v>89.19945199999999</v>
+        <v>88.75692459999999</v>
       </c>
       <c r="O22">
-        <v>26.7598356</v>
+        <v>26.62707738</v>
       </c>
       <c r="P22">
-        <v>62.43961639999999</v>
+        <v>62.12984721999999</v>
       </c>
       <c r="Q22">
-        <v>161.6396164</v>
+        <v>161.32984722</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1231035777852619</v>
+        <v>0.123832267583938</v>
       </c>
       <c r="T22">
-        <v>0.747584678947067</v>
+        <v>0.7546316662250491</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.07841006003244</v>
+        <v>10.55086672384042</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.105442091391311</v>
+        <v>0.1051493205544125</v>
       </c>
       <c r="C23">
-        <v>769.1226435260342</v>
+        <v>764.9326587205212</v>
       </c>
       <c r="D23">
-        <v>882.4256435260342</v>
+        <v>886.7786587205212</v>
       </c>
       <c r="E23">
-        <v>42.60299999999998</v>
+        <v>51.14599999999999</v>
       </c>
       <c r="F23">
-        <v>179.403</v>
+        <v>187.946</v>
       </c>
       <c r="G23">
         <v>66.09999999999999</v>
@@ -3173,28 +3173,28 @@
         <v>98.05</v>
       </c>
       <c r="M23">
-        <v>9.293075399999999</v>
+        <v>9.735602800000001</v>
       </c>
       <c r="N23">
-        <v>88.75692459999999</v>
+        <v>88.3143972</v>
       </c>
       <c r="O23">
-        <v>26.62707738</v>
+        <v>26.49431916</v>
       </c>
       <c r="P23">
-        <v>62.12984721999999</v>
+        <v>61.82007804</v>
       </c>
       <c r="Q23">
-        <v>161.32984722</v>
+        <v>161.02007804</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.123832267583938</v>
+        <v>0.1245796417364262</v>
       </c>
       <c r="T23">
-        <v>0.754631666225049</v>
+        <v>0.7618593454845178</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.55086672384042</v>
+        <v>10.07128187275676</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1051493205544125</v>
+        <v>0.1051302497175139</v>
       </c>
       <c r="C24">
-        <v>764.9326587205212</v>
+        <v>756.6747006889285</v>
       </c>
       <c r="D24">
-        <v>886.7786587205212</v>
+        <v>887.0637006889285</v>
       </c>
       <c r="E24">
-        <v>51.14599999999999</v>
+        <v>59.68899999999999</v>
       </c>
       <c r="F24">
-        <v>187.946</v>
+        <v>196.489</v>
       </c>
       <c r="G24">
         <v>66.09999999999999</v>
@@ -3255,45 +3255,45 @@
         <v>98.05</v>
       </c>
       <c r="M24">
-        <v>9.735602800000001</v>
+        <v>10.5121615</v>
       </c>
       <c r="N24">
-        <v>88.3143972</v>
+        <v>87.53783849999999</v>
       </c>
       <c r="O24">
-        <v>26.49431916</v>
+        <v>26.26135155</v>
       </c>
       <c r="P24">
-        <v>61.82007804</v>
+        <v>61.27648694999999</v>
       </c>
       <c r="Q24">
-        <v>161.02007804</v>
+        <v>160.47648695</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1245796417364262</v>
+        <v>0.1253464282045635</v>
       </c>
       <c r="T24">
-        <v>0.7618593454845178</v>
+        <v>0.7692747566728039</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>10.07128187275676</v>
+        <v>9.327292013160186</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1051302497175139</v>
+        <v>0.1048493788806154</v>
       </c>
       <c r="C25">
-        <v>756.6747006889285</v>
+        <v>752.351056230306</v>
       </c>
       <c r="D25">
-        <v>887.0637006889285</v>
+        <v>891.283056230306</v>
       </c>
       <c r="E25">
-        <v>59.68899999999999</v>
+        <v>68.232</v>
       </c>
       <c r="F25">
-        <v>196.489</v>
+        <v>205.032</v>
       </c>
       <c r="G25">
         <v>66.09999999999999</v>
@@ -3337,28 +3337,28 @@
         <v>98.05</v>
       </c>
       <c r="M25">
-        <v>10.5121615</v>
+        <v>10.969212</v>
       </c>
       <c r="N25">
-        <v>87.53783849999999</v>
+        <v>87.080788</v>
       </c>
       <c r="O25">
-        <v>26.26135155</v>
+        <v>26.1242364</v>
       </c>
       <c r="P25">
-        <v>61.27648694999999</v>
+        <v>60.9565516</v>
       </c>
       <c r="Q25">
-        <v>160.47648695</v>
+        <v>160.1565516</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1253464282045635</v>
+        <v>0.1261333932639676</v>
       </c>
       <c r="T25">
-        <v>0.7692747566728039</v>
+        <v>0.7768853102607819</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.327292013160186</v>
+        <v>8.938654845945177</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1048493788806154</v>
+        <v>0.1045685080437168</v>
       </c>
       <c r="C26">
-        <v>752.3510562303061</v>
+        <v>748.0677426890923</v>
       </c>
       <c r="D26">
-        <v>891.283056230306</v>
+        <v>895.5427426890923</v>
       </c>
       <c r="E26">
-        <v>68.23199999999997</v>
+        <v>76.77499999999998</v>
       </c>
       <c r="F26">
-        <v>205.032</v>
+        <v>213.575</v>
       </c>
       <c r="G26">
         <v>66.09999999999999</v>
@@ -3419,28 +3419,28 @@
         <v>98.05</v>
       </c>
       <c r="M26">
-        <v>10.969212</v>
+        <v>11.4262625</v>
       </c>
       <c r="N26">
-        <v>87.080788</v>
+        <v>86.6237375</v>
       </c>
       <c r="O26">
-        <v>26.1242364</v>
+        <v>25.98712125</v>
       </c>
       <c r="P26">
-        <v>60.9565516</v>
+        <v>60.63661625</v>
       </c>
       <c r="Q26">
-        <v>160.1565516</v>
+        <v>159.83661625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1261333932639676</v>
+        <v>0.1269413440582891</v>
       </c>
       <c r="T26">
-        <v>0.7768853102607819</v>
+        <v>0.7846988119444391</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.938654845945178</v>
+        <v>8.581108652107371</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1045685080437168</v>
+        <v>0.1042876372068183</v>
       </c>
       <c r="C27">
-        <v>748.0677426890923</v>
+        <v>743.825341099797</v>
       </c>
       <c r="D27">
-        <v>895.5427426890923</v>
+        <v>899.8433410997969</v>
       </c>
       <c r="E27">
-        <v>76.77499999999998</v>
+        <v>85.31799999999998</v>
       </c>
       <c r="F27">
-        <v>213.575</v>
+        <v>222.118</v>
       </c>
       <c r="G27">
         <v>66.09999999999999</v>
@@ -3501,28 +3501,28 @@
         <v>98.05</v>
       </c>
       <c r="M27">
-        <v>11.4262625</v>
+        <v>11.883313</v>
       </c>
       <c r="N27">
-        <v>86.6237375</v>
+        <v>86.166687</v>
       </c>
       <c r="O27">
-        <v>25.98712125</v>
+        <v>25.8500061</v>
       </c>
       <c r="P27">
-        <v>60.63661625</v>
+        <v>60.31668089999999</v>
       </c>
       <c r="Q27">
-        <v>159.83661625</v>
+        <v>159.5166809</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1269413440582891</v>
+        <v>0.1277711313605653</v>
       </c>
       <c r="T27">
-        <v>0.7846988119444391</v>
+        <v>0.7927234893492763</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.581108652107371</v>
+        <v>8.251066011641704</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1042876372068183</v>
+        <v>0.1040067663699198</v>
       </c>
       <c r="C28">
-        <v>743.825341099797</v>
+        <v>739.6244437118203</v>
       </c>
       <c r="D28">
-        <v>899.8433410997969</v>
+        <v>904.1854437118203</v>
       </c>
       <c r="E28">
-        <v>85.31799999999998</v>
+        <v>93.86099999999999</v>
       </c>
       <c r="F28">
-        <v>222.118</v>
+        <v>230.661</v>
       </c>
       <c r="G28">
         <v>66.09999999999999</v>
@@ -3583,28 +3583,28 @@
         <v>98.05</v>
       </c>
       <c r="M28">
-        <v>11.883313</v>
+        <v>12.3403635</v>
       </c>
       <c r="N28">
-        <v>86.166687</v>
+        <v>85.7096365</v>
       </c>
       <c r="O28">
-        <v>25.8500061</v>
+        <v>25.71289095</v>
       </c>
       <c r="P28">
-        <v>60.31668089999999</v>
+        <v>59.99674555</v>
       </c>
       <c r="Q28">
-        <v>159.5166809</v>
+        <v>159.19674555</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1277711313605653</v>
+        <v>0.1286236525615339</v>
       </c>
       <c r="T28">
-        <v>0.7927234893492763</v>
+        <v>0.8009680209295886</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.251066011641704</v>
+        <v>7.945470974173491</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1040067663699198</v>
+        <v>0.1037258955330212</v>
       </c>
       <c r="C29">
-        <v>739.6244437118203</v>
+        <v>735.46565426135</v>
       </c>
       <c r="D29">
-        <v>904.1854437118203</v>
+        <v>908.56965426135</v>
       </c>
       <c r="E29">
-        <v>93.86099999999999</v>
+        <v>102.404</v>
       </c>
       <c r="F29">
-        <v>230.661</v>
+        <v>239.204</v>
       </c>
       <c r="G29">
         <v>66.09999999999999</v>
@@ -3665,28 +3665,28 @@
         <v>98.05</v>
       </c>
       <c r="M29">
-        <v>12.3403635</v>
+        <v>12.797414</v>
       </c>
       <c r="N29">
-        <v>85.7096365</v>
+        <v>85.25258599999999</v>
       </c>
       <c r="O29">
-        <v>25.71289095</v>
+        <v>25.5757758</v>
       </c>
       <c r="P29">
-        <v>59.99674555</v>
+        <v>59.67681019999999</v>
       </c>
       <c r="Q29">
-        <v>159.19674555</v>
+        <v>158.8768102</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1286236525615339</v>
+        <v>0.1294998549069739</v>
       </c>
       <c r="T29">
-        <v>0.8009680209295886</v>
+        <v>0.8094415672760205</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.945470974173491</v>
+        <v>7.661704153667295</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1037258955330212</v>
+        <v>0.1036074246961227</v>
       </c>
       <c r="C30">
-        <v>735.46565426135</v>
+        <v>728.7846816373622</v>
       </c>
       <c r="D30">
-        <v>908.56965426135</v>
+        <v>910.4316816373622</v>
       </c>
       <c r="E30">
-        <v>102.404</v>
+        <v>110.947</v>
       </c>
       <c r="F30">
-        <v>239.204</v>
+        <v>247.747</v>
       </c>
       <c r="G30">
         <v>66.09999999999999</v>
@@ -3747,45 +3747,45 @@
         <v>98.05</v>
       </c>
       <c r="M30">
-        <v>12.797414</v>
+        <v>13.4526621</v>
       </c>
       <c r="N30">
-        <v>85.25258599999999</v>
+        <v>84.5973379</v>
       </c>
       <c r="O30">
-        <v>25.5757758</v>
+        <v>25.37920137</v>
       </c>
       <c r="P30">
-        <v>59.67681019999999</v>
+        <v>59.21813653</v>
       </c>
       <c r="Q30">
-        <v>158.8768102</v>
+        <v>158.41813653</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1294998549069739</v>
+        <v>0.1304007390086235</v>
       </c>
       <c r="T30">
-        <v>0.8094415672760205</v>
+        <v>0.818153805068831</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.661704153667295</v>
+        <v>7.288520240168672</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1036074246961227</v>
+        <v>0.1033321538592241</v>
       </c>
       <c r="C31">
-        <v>728.7846816373623</v>
+        <v>724.5977725210184</v>
       </c>
       <c r="D31">
-        <v>910.4316816373622</v>
+        <v>914.7877725210184</v>
       </c>
       <c r="E31">
-        <v>110.9469999999999</v>
+        <v>119.49</v>
       </c>
       <c r="F31">
-        <v>247.747</v>
+        <v>256.29</v>
       </c>
       <c r="G31">
         <v>66.09999999999999</v>
@@ -3829,28 +3829,28 @@
         <v>98.05</v>
       </c>
       <c r="M31">
-        <v>13.4526621</v>
+        <v>13.916547</v>
       </c>
       <c r="N31">
-        <v>84.5973379</v>
+        <v>84.133453</v>
       </c>
       <c r="O31">
-        <v>25.37920137</v>
+        <v>25.2400359</v>
       </c>
       <c r="P31">
-        <v>59.21813653</v>
+        <v>58.89341710000001</v>
       </c>
       <c r="Q31">
-        <v>158.41813653</v>
+        <v>158.0934171</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1304007390086235</v>
+        <v>0.1313273626560345</v>
       </c>
       <c r="T31">
-        <v>0.818153805068831</v>
+        <v>0.8271149639414359</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.288520240168674</v>
+        <v>7.045569565496384</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1033321538592241</v>
+        <v>0.1030568830223256</v>
       </c>
       <c r="C32">
-        <v>724.5977725210184</v>
+        <v>720.4527484923652</v>
       </c>
       <c r="D32">
-        <v>914.7877725210184</v>
+        <v>919.1857484923652</v>
       </c>
       <c r="E32">
-        <v>119.49</v>
+        <v>128.033</v>
       </c>
       <c r="F32">
-        <v>256.29</v>
+        <v>264.833</v>
       </c>
       <c r="G32">
         <v>66.09999999999999</v>
@@ -3911,28 +3911,28 @@
         <v>98.05</v>
       </c>
       <c r="M32">
-        <v>13.916547</v>
+        <v>14.3804319</v>
       </c>
       <c r="N32">
-        <v>84.133453</v>
+        <v>83.66956809999999</v>
       </c>
       <c r="O32">
-        <v>25.2400359</v>
+        <v>25.10087043</v>
       </c>
       <c r="P32">
-        <v>58.89341710000001</v>
+        <v>58.56869766999999</v>
       </c>
       <c r="Q32">
-        <v>158.0934171</v>
+        <v>157.76869767</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1313273626560345</v>
+        <v>0.1322808449598922</v>
       </c>
       <c r="T32">
-        <v>0.8271149639414359</v>
+        <v>0.8363358665494786</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.045569565496384</v>
+        <v>6.818293127899726</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1030568830223256</v>
+        <v>0.102781612185427</v>
       </c>
       <c r="C33">
-        <v>720.4527484923652</v>
+        <v>716.3502165758119</v>
       </c>
       <c r="D33">
-        <v>919.1857484923652</v>
+        <v>923.6262165758119</v>
       </c>
       <c r="E33">
-        <v>128.033</v>
+        <v>136.576</v>
       </c>
       <c r="F33">
-        <v>264.833</v>
+        <v>273.376</v>
       </c>
       <c r="G33">
         <v>66.09999999999999</v>
@@ -3993,28 +3993,28 @@
         <v>98.05</v>
       </c>
       <c r="M33">
-        <v>14.3804319</v>
+        <v>14.8443168</v>
       </c>
       <c r="N33">
-        <v>83.66956809999999</v>
+        <v>83.2056832</v>
       </c>
       <c r="O33">
-        <v>25.10087043</v>
+        <v>24.96170496</v>
       </c>
       <c r="P33">
-        <v>58.56869766999999</v>
+        <v>58.24397824</v>
       </c>
       <c r="Q33">
-        <v>157.76869767</v>
+        <v>157.44397824</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1322808449598922</v>
+        <v>0.1332623708609221</v>
       </c>
       <c r="T33">
-        <v>0.8363358665494786</v>
+        <v>0.845827972175405</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.818293127899726</v>
+        <v>6.60522146765286</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.102781612185427</v>
+        <v>0.1025063413485285</v>
       </c>
       <c r="C34">
-        <v>716.3502165758119</v>
+        <v>712.2907955825337</v>
       </c>
       <c r="D34">
-        <v>923.6262165758119</v>
+        <v>928.1097955825337</v>
       </c>
       <c r="E34">
-        <v>136.576</v>
+        <v>145.119</v>
       </c>
       <c r="F34">
-        <v>273.376</v>
+        <v>281.919</v>
       </c>
       <c r="G34">
         <v>66.09999999999999</v>
@@ -4075,28 +4075,28 @@
         <v>98.05</v>
       </c>
       <c r="M34">
-        <v>14.8443168</v>
+        <v>15.3082017</v>
       </c>
       <c r="N34">
-        <v>83.2056832</v>
+        <v>82.7417983</v>
       </c>
       <c r="O34">
-        <v>24.96170496</v>
+        <v>24.82253949</v>
       </c>
       <c r="P34">
-        <v>58.24397824</v>
+        <v>57.91925881</v>
       </c>
       <c r="Q34">
-        <v>157.44397824</v>
+        <v>157.11925881</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1332623708609221</v>
+        <v>0.1342731960425799</v>
       </c>
       <c r="T34">
-        <v>0.845827972175405</v>
+        <v>0.8556034242379262</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.60522146765286</v>
+        <v>6.405063241360349</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1025063413485285</v>
+        <v>0.10223107051163</v>
       </c>
       <c r="C35">
-        <v>712.2907955825337</v>
+        <v>708.2751163979535</v>
       </c>
       <c r="D35">
-        <v>928.1097955825337</v>
+        <v>932.6371163979535</v>
       </c>
       <c r="E35">
-        <v>145.119</v>
+        <v>153.662</v>
       </c>
       <c r="F35">
-        <v>281.919</v>
+        <v>290.462</v>
       </c>
       <c r="G35">
         <v>66.09999999999999</v>
@@ -4157,28 +4157,28 @@
         <v>98.05</v>
       </c>
       <c r="M35">
-        <v>15.3082017</v>
+        <v>15.7720866</v>
       </c>
       <c r="N35">
-        <v>82.7417983</v>
+        <v>82.2779134</v>
       </c>
       <c r="O35">
-        <v>24.82253949</v>
+        <v>24.68337402</v>
       </c>
       <c r="P35">
-        <v>57.91925881</v>
+        <v>57.59453938</v>
       </c>
       <c r="Q35">
-        <v>157.11925881</v>
+        <v>156.79453938</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1342731960425799</v>
+        <v>0.1353146522903484</v>
       </c>
       <c r="T35">
-        <v>0.8556034242379262</v>
+        <v>0.8656751021205238</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.405063241360349</v>
+        <v>6.216679028379162</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.10223107051163</v>
+        <v>0.1022007996747314</v>
       </c>
       <c r="C36">
-        <v>708.2751163979535</v>
+        <v>700.2326714645272</v>
       </c>
       <c r="D36">
-        <v>932.6371163979535</v>
+        <v>933.1376714645272</v>
       </c>
       <c r="E36">
-        <v>153.662</v>
+        <v>162.205</v>
       </c>
       <c r="F36">
-        <v>290.462</v>
+        <v>299.005</v>
       </c>
       <c r="G36">
         <v>66.09999999999999</v>
@@ -4239,45 +4239,45 @@
         <v>98.05</v>
       </c>
       <c r="M36">
-        <v>15.7720866</v>
+        <v>16.5349765</v>
       </c>
       <c r="N36">
-        <v>82.2779134</v>
+        <v>81.5150235</v>
       </c>
       <c r="O36">
-        <v>24.68337402</v>
+        <v>24.45450705</v>
       </c>
       <c r="P36">
-        <v>57.59453938</v>
+        <v>57.06051644999999</v>
       </c>
       <c r="Q36">
-        <v>156.79453938</v>
+        <v>156.26051645</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1353146522903484</v>
+        <v>0.1363881533457407</v>
       </c>
       <c r="T36">
-        <v>0.8656751021205238</v>
+        <v>0.8760566777841243</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.216679028379162</v>
+        <v>5.929854209348287</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1022007996747314</v>
+        <v>0.1019325288378329</v>
       </c>
       <c r="C37">
-        <v>700.2326714645272</v>
+        <v>696.1493605120057</v>
       </c>
       <c r="D37">
-        <v>933.1376714645272</v>
+        <v>937.5973605120057</v>
       </c>
       <c r="E37">
-        <v>162.205</v>
+        <v>170.748</v>
       </c>
       <c r="F37">
-        <v>299.005</v>
+        <v>307.548</v>
       </c>
       <c r="G37">
         <v>66.09999999999999</v>
@@ -4321,28 +4321,28 @@
         <v>98.05</v>
       </c>
       <c r="M37">
-        <v>16.5349765</v>
+        <v>17.0074044</v>
       </c>
       <c r="N37">
-        <v>81.5150235</v>
+        <v>81.0425956</v>
       </c>
       <c r="O37">
-        <v>24.45450705</v>
+        <v>24.31277868</v>
       </c>
       <c r="P37">
-        <v>57.06051644999999</v>
+        <v>56.72981692</v>
       </c>
       <c r="Q37">
-        <v>156.26051645</v>
+        <v>155.92981692</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1363881533457407</v>
+        <v>0.1374952013091139</v>
       </c>
       <c r="T37">
-        <v>0.8760566777841243</v>
+        <v>0.8867626776872125</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.929854209348287</v>
+        <v>5.765136036866389</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1019325288378329</v>
+        <v>0.1016642580009343</v>
       </c>
       <c r="C38">
-        <v>696.1493605120058</v>
+        <v>692.1088821166823</v>
       </c>
       <c r="D38">
-        <v>937.5973605120057</v>
+        <v>942.0998821166821</v>
       </c>
       <c r="E38">
-        <v>170.7479999999999</v>
+        <v>179.2909999999999</v>
       </c>
       <c r="F38">
-        <v>307.5479999999999</v>
+        <v>316.091</v>
       </c>
       <c r="G38">
         <v>66.09999999999999</v>
@@ -4403,28 +4403,28 @@
         <v>98.05</v>
       </c>
       <c r="M38">
-        <v>17.0074044</v>
+        <v>17.4798323</v>
       </c>
       <c r="N38">
-        <v>81.0425956</v>
+        <v>80.5701677</v>
       </c>
       <c r="O38">
-        <v>24.31277868</v>
+        <v>24.17105031</v>
       </c>
       <c r="P38">
-        <v>56.72981692</v>
+        <v>56.39911739</v>
       </c>
       <c r="Q38">
-        <v>155.92981692</v>
+        <v>155.59911739</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1374952013091139</v>
+        <v>0.1386373936522767</v>
       </c>
       <c r="T38">
-        <v>0.8867626776872125</v>
+        <v>0.8978085506030969</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.76513603686639</v>
+        <v>5.609321549383515</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1016642580009343</v>
+        <v>0.1013959871640358</v>
       </c>
       <c r="C39">
-        <v>692.1088821166823</v>
+        <v>688.1118563265071</v>
       </c>
       <c r="D39">
-        <v>942.0998821166821</v>
+        <v>946.6458563265071</v>
       </c>
       <c r="E39">
-        <v>179.2909999999999</v>
+        <v>187.834</v>
       </c>
       <c r="F39">
-        <v>316.091</v>
+        <v>324.634</v>
       </c>
       <c r="G39">
         <v>66.09999999999999</v>
@@ -4485,28 +4485,28 @@
         <v>98.05</v>
       </c>
       <c r="M39">
-        <v>17.4798323</v>
+        <v>17.9522602</v>
       </c>
       <c r="N39">
-        <v>80.5701677</v>
+        <v>80.0977398</v>
       </c>
       <c r="O39">
-        <v>24.17105031</v>
+        <v>24.02932194</v>
       </c>
       <c r="P39">
-        <v>56.39911739</v>
+        <v>56.06841786</v>
       </c>
       <c r="Q39">
-        <v>155.59911739</v>
+        <v>155.26841786</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1386373936522767</v>
+        <v>0.1398164309097352</v>
       </c>
       <c r="T39">
-        <v>0.8978085506030969</v>
+        <v>0.9092107420001391</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.609321549383515</v>
+        <v>5.461707824399737</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1013959871640358</v>
+        <v>0.1011277163271373</v>
       </c>
       <c r="C40">
-        <v>688.1118563265071</v>
+        <v>684.1589152152866</v>
       </c>
       <c r="D40">
-        <v>946.6458563265071</v>
+        <v>951.2359152152866</v>
       </c>
       <c r="E40">
-        <v>187.834</v>
+        <v>196.377</v>
       </c>
       <c r="F40">
-        <v>324.634</v>
+        <v>333.177</v>
       </c>
       <c r="G40">
         <v>66.09999999999999</v>
@@ -4567,28 +4567,28 @@
         <v>98.05</v>
       </c>
       <c r="M40">
-        <v>17.9522602</v>
+        <v>18.4246881</v>
       </c>
       <c r="N40">
-        <v>80.0977398</v>
+        <v>79.6253119</v>
       </c>
       <c r="O40">
-        <v>24.02932194</v>
+        <v>23.88759357</v>
       </c>
       <c r="P40">
-        <v>56.06841786</v>
+        <v>55.73771833</v>
       </c>
       <c r="Q40">
-        <v>155.26841786</v>
+        <v>154.93771833</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1398164309097352</v>
+        <v>0.1410341251264545</v>
       </c>
       <c r="T40">
-        <v>0.9092107420001391</v>
+        <v>0.9209867757380679</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.461707824399737</v>
+        <v>5.321664034030514</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1011277163271373</v>
+        <v>0.1008594454902387</v>
       </c>
       <c r="C41">
-        <v>684.1589152152866</v>
+        <v>680.2507031756556</v>
       </c>
       <c r="D41">
-        <v>951.2359152152866</v>
+        <v>955.8707031756556</v>
       </c>
       <c r="E41">
-        <v>196.377</v>
+        <v>204.92</v>
       </c>
       <c r="F41">
-        <v>333.177</v>
+        <v>341.72</v>
       </c>
       <c r="G41">
         <v>66.09999999999999</v>
@@ -4649,28 +4649,28 @@
         <v>98.05</v>
       </c>
       <c r="M41">
-        <v>18.4246881</v>
+        <v>18.897116</v>
       </c>
       <c r="N41">
-        <v>79.6253119</v>
+        <v>79.152884</v>
       </c>
       <c r="O41">
-        <v>23.88759357</v>
+        <v>23.7458652</v>
       </c>
       <c r="P41">
-        <v>55.73771833</v>
+        <v>55.4070188</v>
       </c>
       <c r="Q41">
-        <v>154.93771833</v>
+        <v>154.6070188</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1410341251264545</v>
+        <v>0.1422924091503979</v>
       </c>
       <c r="T41">
-        <v>0.9209867757380679</v>
+        <v>0.9331553439339276</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.321664034030514</v>
+        <v>5.18862243317975</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1008594454902387</v>
+        <v>0.1005911746533402</v>
       </c>
       <c r="C42">
-        <v>680.2507031756556</v>
+        <v>676.3878772206573</v>
       </c>
       <c r="D42">
-        <v>955.8707031756556</v>
+        <v>960.5508772206574</v>
       </c>
       <c r="E42">
-        <v>204.92</v>
+        <v>213.463</v>
       </c>
       <c r="F42">
-        <v>341.72</v>
+        <v>350.263</v>
       </c>
       <c r="G42">
         <v>66.09999999999999</v>
@@ -4731,28 +4731,28 @@
         <v>98.05</v>
       </c>
       <c r="M42">
-        <v>18.897116</v>
+        <v>19.3695439</v>
       </c>
       <c r="N42">
-        <v>79.152884</v>
+        <v>78.68045609999999</v>
       </c>
       <c r="O42">
-        <v>23.7458652</v>
+        <v>23.60413682999999</v>
       </c>
       <c r="P42">
-        <v>55.4070188</v>
+        <v>55.07631926999999</v>
       </c>
       <c r="Q42">
-        <v>154.6070188</v>
+        <v>154.27631927</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1422924091503979</v>
+        <v>0.1435933468700681</v>
       </c>
       <c r="T42">
-        <v>0.9331553439339276</v>
+        <v>0.9457364059669351</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.18862243317975</v>
+        <v>5.062070666516829</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1005911746533402</v>
+        <v>0.1003229038164416</v>
       </c>
       <c r="C43">
-        <v>676.3878772206573</v>
+        <v>672.571107294227</v>
       </c>
       <c r="D43">
-        <v>960.5508772206574</v>
+        <v>965.2771072942271</v>
       </c>
       <c r="E43">
-        <v>213.463</v>
+        <v>222.006</v>
       </c>
       <c r="F43">
-        <v>350.263</v>
+        <v>358.806</v>
       </c>
       <c r="G43">
         <v>66.09999999999999</v>
@@ -4813,28 +4813,28 @@
         <v>98.05</v>
       </c>
       <c r="M43">
-        <v>19.3695439</v>
+        <v>19.8419718</v>
       </c>
       <c r="N43">
-        <v>78.68045609999999</v>
+        <v>78.2080282</v>
       </c>
       <c r="O43">
-        <v>23.60413682999999</v>
+        <v>23.46240846</v>
       </c>
       <c r="P43">
-        <v>55.07631926999999</v>
+        <v>54.74561974</v>
       </c>
       <c r="Q43">
-        <v>154.27631927</v>
+        <v>153.94561974</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1435933468700681</v>
+        <v>0.1449391445111063</v>
       </c>
       <c r="T43">
-        <v>0.9457364059669351</v>
+        <v>0.9587512977252187</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.062070666516829</v>
+        <v>4.941545174456905</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1003229038164416</v>
+        <v>0.1000546329795431</v>
       </c>
       <c r="C44">
-        <v>672.571107294227</v>
+        <v>668.8010765908853</v>
       </c>
       <c r="D44">
-        <v>965.2771072942271</v>
+        <v>970.0500765908852</v>
       </c>
       <c r="E44">
-        <v>222.006</v>
+        <v>230.549</v>
       </c>
       <c r="F44">
-        <v>358.806</v>
+        <v>367.349</v>
       </c>
       <c r="G44">
         <v>66.09999999999999</v>
@@ -4895,28 +4895,28 @@
         <v>98.05</v>
       </c>
       <c r="M44">
-        <v>19.8419718</v>
+        <v>20.3143997</v>
       </c>
       <c r="N44">
-        <v>78.2080282</v>
+        <v>77.7356003</v>
       </c>
       <c r="O44">
-        <v>23.46240846</v>
+        <v>23.32068009</v>
       </c>
       <c r="P44">
-        <v>54.74561974</v>
+        <v>54.41492021000001</v>
       </c>
       <c r="Q44">
-        <v>153.94561974</v>
+        <v>153.61492021</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1449391445111063</v>
+        <v>0.1463321631220054</v>
       </c>
       <c r="T44">
-        <v>0.9587512977252186</v>
+        <v>0.972222852352214</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.941545174456905</v>
+        <v>4.826625519236978</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1000546329795431</v>
+        <v>0.09978636214264458</v>
       </c>
       <c r="C45">
-        <v>668.8010765908853</v>
+        <v>665.078481884965</v>
       </c>
       <c r="D45">
-        <v>970.0500765908852</v>
+        <v>974.8704818849651</v>
       </c>
       <c r="E45">
-        <v>230.549</v>
+        <v>239.092</v>
       </c>
       <c r="F45">
-        <v>367.349</v>
+        <v>375.892</v>
       </c>
       <c r="G45">
         <v>66.09999999999999</v>
@@ -4977,28 +4977,28 @@
         <v>98.05</v>
       </c>
       <c r="M45">
-        <v>20.3143997</v>
+        <v>20.7868276</v>
       </c>
       <c r="N45">
-        <v>77.7356003</v>
+        <v>77.2631724</v>
       </c>
       <c r="O45">
-        <v>23.32068009</v>
+        <v>23.17895172</v>
       </c>
       <c r="P45">
-        <v>54.41492021000001</v>
+        <v>54.08422068</v>
       </c>
       <c r="Q45">
-        <v>153.61492021</v>
+        <v>153.28422068</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1463321631220054</v>
+        <v>0.1477749323975796</v>
       </c>
       <c r="T45">
-        <v>0.972222852352214</v>
+        <v>0.9861755339301734</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.826625519236978</v>
+        <v>4.716929484708865</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09978636214264458</v>
+        <v>0.09951809130574604</v>
       </c>
       <c r="C46">
-        <v>665.078481884965</v>
+        <v>661.4040338697037</v>
       </c>
       <c r="D46">
-        <v>974.8704818849651</v>
+        <v>979.7390338697037</v>
       </c>
       <c r="E46">
-        <v>239.092</v>
+        <v>247.635</v>
       </c>
       <c r="F46">
-        <v>375.892</v>
+        <v>384.435</v>
       </c>
       <c r="G46">
         <v>66.09999999999999</v>
@@ -5059,28 +5059,28 @@
         <v>98.05</v>
       </c>
       <c r="M46">
-        <v>20.7868276</v>
+        <v>21.2592555</v>
       </c>
       <c r="N46">
-        <v>77.2631724</v>
+        <v>76.79074449999999</v>
       </c>
       <c r="O46">
-        <v>23.17895172</v>
+        <v>23.03722334999999</v>
       </c>
       <c r="P46">
-        <v>54.08422068</v>
+        <v>53.75352115</v>
       </c>
       <c r="Q46">
-        <v>153.28422068</v>
+        <v>152.95352115</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1477749323975796</v>
+        <v>0.1492701660104473</v>
       </c>
       <c r="T46">
-        <v>0.9861755339301734</v>
+        <v>1.000635585747331</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.716929484708865</v>
+        <v>4.612108829493112</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09951809130574604</v>
+        <v>0.09924982046884749</v>
       </c>
       <c r="C47">
-        <v>661.4040338697037</v>
+        <v>657.7784575065443</v>
       </c>
       <c r="D47">
-        <v>979.7390338697037</v>
+        <v>984.6564575065444</v>
       </c>
       <c r="E47">
-        <v>247.635</v>
+        <v>256.178</v>
       </c>
       <c r="F47">
-        <v>384.435</v>
+        <v>392.978</v>
       </c>
       <c r="G47">
         <v>66.09999999999999</v>
@@ -5141,28 +5141,28 @@
         <v>98.05</v>
       </c>
       <c r="M47">
-        <v>21.2592555</v>
+        <v>21.7316834</v>
       </c>
       <c r="N47">
-        <v>76.79074449999999</v>
+        <v>76.3183166</v>
       </c>
       <c r="O47">
-        <v>23.03722334999999</v>
+        <v>22.89549498</v>
       </c>
       <c r="P47">
-        <v>53.75352115</v>
+        <v>53.42282162000001</v>
       </c>
       <c r="Q47">
-        <v>152.95352115</v>
+        <v>152.62282162</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1492701660104473</v>
+        <v>0.1508207786460138</v>
       </c>
       <c r="T47">
-        <v>1.000635585747331</v>
+        <v>1.015631195039199</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.612108829493112</v>
+        <v>4.511845594069348</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09924982046884749</v>
+        <v>0.09980404963194894</v>
       </c>
       <c r="C48">
-        <v>657.7784575065443</v>
+        <v>639.1301908069997</v>
       </c>
       <c r="D48">
-        <v>984.6564575065444</v>
+        <v>974.5511908069998</v>
       </c>
       <c r="E48">
-        <v>256.178</v>
+        <v>264.721</v>
       </c>
       <c r="F48">
-        <v>392.978</v>
+        <v>401.521</v>
       </c>
       <c r="G48">
         <v>66.09999999999999</v>
@@ -5223,45 +5223,45 @@
         <v>98.05</v>
       </c>
       <c r="M48">
-        <v>21.7316834</v>
+        <v>23.2079138</v>
       </c>
       <c r="N48">
-        <v>76.3183166</v>
+        <v>74.8420862</v>
       </c>
       <c r="O48">
-        <v>22.89549498</v>
+        <v>22.45262586</v>
       </c>
       <c r="P48">
-        <v>53.42282162000001</v>
+        <v>52.38946034</v>
       </c>
       <c r="Q48">
-        <v>152.62282162</v>
+        <v>151.58946034</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1508207786460138</v>
+        <v>0.1524299049659414</v>
       </c>
       <c r="T48">
-        <v>1.015631195039199</v>
+        <v>1.031192676379816</v>
       </c>
       <c r="U48">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V48">
         <v>0.3</v>
       </c>
       <c r="W48">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.511845594069348</v>
+        <v>4.224851955456677</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09980404963194894</v>
+        <v>0.0995532787950504</v>
       </c>
       <c r="C49">
-        <v>639.1301908069997</v>
+        <v>635.1336858896707</v>
       </c>
       <c r="D49">
-        <v>974.5511908069998</v>
+        <v>979.0976858896709</v>
       </c>
       <c r="E49">
-        <v>264.721</v>
+        <v>273.264</v>
       </c>
       <c r="F49">
-        <v>401.521</v>
+        <v>410.064</v>
       </c>
       <c r="G49">
         <v>66.09999999999999</v>
@@ -5305,28 +5305,28 @@
         <v>98.05</v>
       </c>
       <c r="M49">
-        <v>23.2079138</v>
+        <v>23.7016992</v>
       </c>
       <c r="N49">
-        <v>74.8420862</v>
+        <v>74.34830079999999</v>
       </c>
       <c r="O49">
-        <v>22.45262586</v>
+        <v>22.30449024</v>
       </c>
       <c r="P49">
-        <v>52.38946034</v>
+        <v>52.04381056</v>
       </c>
       <c r="Q49">
-        <v>151.58946034</v>
+        <v>151.24381056</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1524299049659414</v>
+        <v>0.1541009207597123</v>
       </c>
       <c r="T49">
-        <v>1.031192676379816</v>
+        <v>1.047352676233534</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.224851955456677</v>
+        <v>4.136834206384663</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0995532787950504</v>
+        <v>0.09930250795815185</v>
       </c>
       <c r="C50">
-        <v>635.1336858896708</v>
+        <v>631.1798005959952</v>
       </c>
       <c r="D50">
-        <v>979.0976858896709</v>
+        <v>983.6868005959951</v>
       </c>
       <c r="E50">
-        <v>273.264</v>
+        <v>281.807</v>
       </c>
       <c r="F50">
-        <v>410.064</v>
+        <v>418.607</v>
       </c>
       <c r="G50">
         <v>66.09999999999999</v>
@@ -5387,28 +5387,28 @@
         <v>98.05</v>
       </c>
       <c r="M50">
-        <v>23.7016992</v>
+        <v>24.1954846</v>
       </c>
       <c r="N50">
-        <v>74.3483008</v>
+        <v>73.8545154</v>
       </c>
       <c r="O50">
-        <v>22.30449024</v>
+        <v>22.15635462</v>
       </c>
       <c r="P50">
-        <v>52.04381056</v>
+        <v>51.69816077999999</v>
       </c>
       <c r="Q50">
-        <v>151.24381056</v>
+        <v>150.89816078</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1541009207597123</v>
+        <v>0.1558374665846115</v>
       </c>
       <c r="T50">
-        <v>1.047352676233534</v>
+        <v>1.064146401571711</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.136834206384663</v>
+        <v>4.052409018499262</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09930250795815185</v>
+        <v>0.1002767371212533</v>
       </c>
       <c r="C51">
-        <v>631.1798005959952</v>
+        <v>605.0451381885065</v>
       </c>
       <c r="D51">
-        <v>983.6868005959951</v>
+        <v>966.0951381885064</v>
       </c>
       <c r="E51">
-        <v>281.807</v>
+        <v>290.35</v>
       </c>
       <c r="F51">
-        <v>418.607</v>
+        <v>427.15</v>
       </c>
       <c r="G51">
         <v>66.09999999999999</v>
@@ -5469,45 +5469,45 @@
         <v>98.05</v>
       </c>
       <c r="M51">
-        <v>24.1954846</v>
+        <v>26.184295</v>
       </c>
       <c r="N51">
-        <v>73.8545154</v>
+        <v>71.86570499999999</v>
       </c>
       <c r="O51">
-        <v>22.15635462</v>
+        <v>21.5597115</v>
       </c>
       <c r="P51">
-        <v>51.69816077999999</v>
+        <v>50.3059935</v>
       </c>
       <c r="Q51">
-        <v>150.89816078</v>
+        <v>149.5059935</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1558374665846115</v>
+        <v>0.1576434742425066</v>
       </c>
       <c r="T51">
-        <v>1.064146401571711</v>
+        <v>1.081611875923416</v>
       </c>
       <c r="U51">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.052409018499262</v>
+        <v>3.744611034973445</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1002767371212533</v>
+        <v>0.1000504662843548</v>
       </c>
       <c r="C52">
-        <v>605.0451381885065</v>
+        <v>600.5315810746877</v>
       </c>
       <c r="D52">
-        <v>966.0951381885064</v>
+        <v>970.1245810746877</v>
       </c>
       <c r="E52">
-        <v>290.35</v>
+        <v>298.893</v>
       </c>
       <c r="F52">
-        <v>427.15</v>
+        <v>435.693</v>
       </c>
       <c r="G52">
         <v>66.09999999999999</v>
@@ -5551,28 +5551,28 @@
         <v>98.05</v>
       </c>
       <c r="M52">
-        <v>26.184295</v>
+        <v>26.7079809</v>
       </c>
       <c r="N52">
-        <v>71.86570499999999</v>
+        <v>71.3420191</v>
       </c>
       <c r="O52">
-        <v>21.5597115</v>
+        <v>21.40260573</v>
       </c>
       <c r="P52">
-        <v>50.3059935</v>
+        <v>49.93941337</v>
       </c>
       <c r="Q52">
-        <v>149.5059935</v>
+        <v>149.13941337</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1576434742425066</v>
+        <v>0.1595231964986832</v>
       </c>
       <c r="T52">
-        <v>1.081611875923416</v>
+        <v>1.099790226779272</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.744611034973445</v>
+        <v>3.671187289189652</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1000504662843548</v>
+        <v>0.09982419544745622</v>
       </c>
       <c r="C53">
-        <v>600.5315810746877</v>
+        <v>596.0517771859401</v>
       </c>
       <c r="D53">
-        <v>970.1245810746877</v>
+        <v>974.1877771859401</v>
       </c>
       <c r="E53">
-        <v>298.893</v>
+        <v>307.436</v>
       </c>
       <c r="F53">
-        <v>435.693</v>
+        <v>444.236</v>
       </c>
       <c r="G53">
         <v>66.09999999999999</v>
@@ -5633,28 +5633,28 @@
         <v>98.05</v>
       </c>
       <c r="M53">
-        <v>26.7079809</v>
+        <v>27.2316668</v>
       </c>
       <c r="N53">
-        <v>71.3420191</v>
+        <v>70.8183332</v>
       </c>
       <c r="O53">
-        <v>21.40260573</v>
+        <v>21.24549996</v>
       </c>
       <c r="P53">
-        <v>49.93941337</v>
+        <v>49.57283323999999</v>
       </c>
       <c r="Q53">
-        <v>149.13941337</v>
+        <v>148.77283324</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1595231964986832</v>
+        <v>0.1614812405155338</v>
       </c>
       <c r="T53">
-        <v>1.099790226779272</v>
+        <v>1.118726008920788</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.671187289189652</v>
+        <v>3.600587533628313</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09982419544745622</v>
+        <v>0.09959792461055769</v>
       </c>
       <c r="C54">
-        <v>596.0517771859401</v>
+        <v>591.6061524143688</v>
       </c>
       <c r="D54">
-        <v>974.1877771859401</v>
+        <v>978.2851524143688</v>
       </c>
       <c r="E54">
-        <v>307.436</v>
+        <v>315.979</v>
       </c>
       <c r="F54">
-        <v>444.236</v>
+        <v>452.779</v>
       </c>
       <c r="G54">
         <v>66.09999999999999</v>
@@ -5715,28 +5715,28 @@
         <v>98.05</v>
       </c>
       <c r="M54">
-        <v>27.2316668</v>
+        <v>27.7553527</v>
       </c>
       <c r="N54">
-        <v>70.8183332</v>
+        <v>70.29464729999999</v>
       </c>
       <c r="O54">
-        <v>21.24549996</v>
+        <v>21.08839419</v>
       </c>
       <c r="P54">
-        <v>49.57283323999999</v>
+        <v>49.20625310999999</v>
       </c>
       <c r="Q54">
-        <v>148.77283324</v>
+        <v>148.40625311</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1614812405155338</v>
+        <v>0.1635226055543781</v>
       </c>
       <c r="T54">
-        <v>1.118726008920788</v>
+        <v>1.138467569025773</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.600587533628313</v>
+        <v>3.532651919786268</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09959792461055769</v>
+        <v>0.1004300537736591</v>
       </c>
       <c r="C55">
-        <v>591.6061524143688</v>
+        <v>568.1618380476301</v>
       </c>
       <c r="D55">
-        <v>978.2851524143688</v>
+        <v>963.3838380476302</v>
       </c>
       <c r="E55">
-        <v>315.979</v>
+        <v>324.522</v>
       </c>
       <c r="F55">
-        <v>452.779</v>
+        <v>461.322</v>
       </c>
       <c r="G55">
         <v>66.09999999999999</v>
@@ -5797,45 +5797,45 @@
         <v>98.05</v>
       </c>
       <c r="M55">
-        <v>27.7553527</v>
+        <v>29.5707402</v>
       </c>
       <c r="N55">
-        <v>70.29464729999999</v>
+        <v>68.47925979999999</v>
       </c>
       <c r="O55">
-        <v>21.08839419</v>
+        <v>20.54377794</v>
       </c>
       <c r="P55">
-        <v>49.20625310999999</v>
+        <v>47.93548186</v>
       </c>
       <c r="Q55">
-        <v>148.40625311</v>
+        <v>147.13548186</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1635226055543781</v>
+        <v>0.1656527255949112</v>
       </c>
       <c r="T55">
-        <v>1.138467569025773</v>
+        <v>1.159067457830975</v>
       </c>
       <c r="U55">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.3</v>
       </c>
       <c r="W55">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.532651919786268</v>
+        <v>3.315777668629343</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1004300537736591</v>
+        <v>0.1002233829367606</v>
       </c>
       <c r="C56">
-        <v>568.1618380476301</v>
+        <v>563.2772534808487</v>
       </c>
       <c r="D56">
-        <v>963.3838380476302</v>
+        <v>967.0422534808488</v>
       </c>
       <c r="E56">
-        <v>324.522</v>
+        <v>333.065</v>
       </c>
       <c r="F56">
-        <v>461.322</v>
+        <v>469.865</v>
       </c>
       <c r="G56">
         <v>66.09999999999999</v>
@@ -5879,28 +5879,28 @@
         <v>98.05</v>
       </c>
       <c r="M56">
-        <v>29.5707402</v>
+        <v>30.1183465</v>
       </c>
       <c r="N56">
-        <v>68.47925979999999</v>
+        <v>67.9316535</v>
       </c>
       <c r="O56">
-        <v>20.54377794</v>
+        <v>20.37949605</v>
       </c>
       <c r="P56">
-        <v>47.93548186</v>
+        <v>47.55215745</v>
       </c>
       <c r="Q56">
-        <v>147.13548186</v>
+        <v>146.75215745</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1656527255949112</v>
+        <v>0.1678775176372458</v>
       </c>
       <c r="T56">
-        <v>1.159067457830975</v>
+        <v>1.180582897249742</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.315777668629343</v>
+        <v>3.255490801926991</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1002233829367606</v>
+        <v>0.1000167120998621</v>
       </c>
       <c r="C57">
-        <v>563.2772534808487</v>
+        <v>558.4205602320777</v>
       </c>
       <c r="D57">
-        <v>967.0422534808488</v>
+        <v>970.7285602320777</v>
       </c>
       <c r="E57">
-        <v>333.065</v>
+        <v>341.608</v>
       </c>
       <c r="F57">
-        <v>469.865</v>
+        <v>478.408</v>
       </c>
       <c r="G57">
         <v>66.09999999999999</v>
@@ -5961,28 +5961,28 @@
         <v>98.05</v>
       </c>
       <c r="M57">
-        <v>30.1183465</v>
+        <v>30.6659528</v>
       </c>
       <c r="N57">
-        <v>67.9316535</v>
+        <v>67.3840472</v>
       </c>
       <c r="O57">
-        <v>20.37949605</v>
+        <v>20.21521416</v>
       </c>
       <c r="P57">
-        <v>47.55215745</v>
+        <v>47.16883304</v>
       </c>
       <c r="Q57">
-        <v>146.75215745</v>
+        <v>146.36883304</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1678775176372458</v>
+        <v>0.1702034365905956</v>
       </c>
       <c r="T57">
-        <v>1.180582897249742</v>
+        <v>1.203076311187543</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.255490801926991</v>
+        <v>3.197357037606866</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1000167120998621</v>
+        <v>0.09981004126296353</v>
       </c>
       <c r="C58">
-        <v>558.4205602320777</v>
+        <v>553.5920784818913</v>
       </c>
       <c r="D58">
-        <v>970.7285602320777</v>
+        <v>974.4430784818913</v>
       </c>
       <c r="E58">
-        <v>341.608</v>
+        <v>350.151</v>
       </c>
       <c r="F58">
-        <v>478.408</v>
+        <v>486.951</v>
       </c>
       <c r="G58">
         <v>66.09999999999999</v>
@@ -6043,28 +6043,28 @@
         <v>98.05</v>
       </c>
       <c r="M58">
-        <v>30.6659528</v>
+        <v>31.2135591</v>
       </c>
       <c r="N58">
-        <v>67.3840472</v>
+        <v>66.83644089999999</v>
       </c>
       <c r="O58">
-        <v>20.21521416</v>
+        <v>20.05093226999999</v>
       </c>
       <c r="P58">
-        <v>47.16883304</v>
+        <v>46.78550863</v>
       </c>
       <c r="Q58">
-        <v>146.36883304</v>
+        <v>145.98550863</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1702034365905956</v>
+        <v>0.1726375378208454</v>
       </c>
       <c r="T58">
-        <v>1.203076311187543</v>
+        <v>1.226615930424777</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.197357037606866</v>
+        <v>3.141263054490956</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09981004126296353</v>
+        <v>0.09960337042606499</v>
       </c>
       <c r="C59">
-        <v>553.5920784818913</v>
+        <v>548.7921333304083</v>
       </c>
       <c r="D59">
-        <v>974.4430784818913</v>
+        <v>978.1861333304084</v>
       </c>
       <c r="E59">
-        <v>350.151</v>
+        <v>358.694</v>
       </c>
       <c r="F59">
-        <v>486.951</v>
+        <v>495.494</v>
       </c>
       <c r="G59">
         <v>66.09999999999999</v>
@@ -6125,28 +6125,28 @@
         <v>98.05</v>
       </c>
       <c r="M59">
-        <v>31.2135591</v>
+        <v>31.7611654</v>
       </c>
       <c r="N59">
-        <v>66.83644089999999</v>
+        <v>66.2888346</v>
       </c>
       <c r="O59">
-        <v>20.05093226999999</v>
+        <v>19.88665038</v>
       </c>
       <c r="P59">
-        <v>46.78550863</v>
+        <v>46.40218422</v>
       </c>
       <c r="Q59">
-        <v>145.98550863</v>
+        <v>145.60218422</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1726375378208454</v>
+        <v>0.1751875486334881</v>
       </c>
       <c r="T59">
-        <v>1.226615930424777</v>
+        <v>1.251276483911403</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.141263054490956</v>
+        <v>3.087103346654906</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09960337042606497</v>
+        <v>0.09939669958916644</v>
       </c>
       <c r="C60">
-        <v>548.7921333304089</v>
+        <v>544.0210548921385</v>
       </c>
       <c r="D60">
-        <v>978.1861333304088</v>
+        <v>981.9580548921385</v>
       </c>
       <c r="E60">
-        <v>358.6939999999999</v>
+        <v>367.2369999999999</v>
       </c>
       <c r="F60">
-        <v>495.4939999999999</v>
+        <v>504.0369999999999</v>
       </c>
       <c r="G60">
         <v>66.09999999999999</v>
@@ -6207,28 +6207,28 @@
         <v>98.05</v>
       </c>
       <c r="M60">
-        <v>31.7611654</v>
+        <v>32.30877169999999</v>
       </c>
       <c r="N60">
-        <v>66.2888346</v>
+        <v>65.7412283</v>
       </c>
       <c r="O60">
-        <v>19.88665038</v>
+        <v>19.72236849</v>
       </c>
       <c r="P60">
-        <v>46.40218422</v>
+        <v>46.01885981</v>
       </c>
       <c r="Q60">
-        <v>145.60218422</v>
+        <v>145.21885981</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.175187548633488</v>
+        <v>0.1778619502174791</v>
       </c>
       <c r="T60">
-        <v>1.251276483911403</v>
+        <v>1.277139991226645</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.087103346654906</v>
+        <v>3.034779561118382</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09939669958916644</v>
+        <v>0.1024660287522679</v>
       </c>
       <c r="C61">
-        <v>544.0210548921385</v>
+        <v>482.2900591707655</v>
       </c>
       <c r="D61">
-        <v>981.9580548921385</v>
+        <v>928.7700591707654</v>
       </c>
       <c r="E61">
-        <v>367.2369999999999</v>
+        <v>375.7799999999999</v>
       </c>
       <c r="F61">
-        <v>504.0369999999999</v>
+        <v>512.5799999999999</v>
       </c>
       <c r="G61">
         <v>66.09999999999999</v>
@@ -6289,45 +6289,45 @@
         <v>98.05</v>
       </c>
       <c r="M61">
-        <v>32.30877169999999</v>
+        <v>36.854502</v>
       </c>
       <c r="N61">
-        <v>65.7412283</v>
+        <v>61.195498</v>
       </c>
       <c r="O61">
-        <v>19.72236849</v>
+        <v>18.3586494</v>
       </c>
       <c r="P61">
-        <v>46.01885981</v>
+        <v>42.8368486</v>
       </c>
       <c r="Q61">
-        <v>145.21885981</v>
+        <v>142.0368486</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1778619502174791</v>
+        <v>0.1806700718806697</v>
       </c>
       <c r="T61">
-        <v>1.277139991226645</v>
+        <v>1.304296673907649</v>
       </c>
       <c r="U61">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V61">
         <v>0.3</v>
       </c>
       <c r="W61">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.034779561118382</v>
+        <v>2.660461943021236</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1024660287522679</v>
+        <v>0.1023139579153694</v>
       </c>
       <c r="C62">
-        <v>482.2900591707655</v>
+        <v>476.2462442463519</v>
       </c>
       <c r="D62">
-        <v>928.7700591707654</v>
+        <v>931.2692442463518</v>
       </c>
       <c r="E62">
-        <v>375.7799999999999</v>
+        <v>384.3229999999999</v>
       </c>
       <c r="F62">
-        <v>512.5799999999999</v>
+        <v>521.1229999999999</v>
       </c>
       <c r="G62">
         <v>66.09999999999999</v>
@@ -6371,28 +6371,28 @@
         <v>98.05</v>
       </c>
       <c r="M62">
-        <v>36.854502</v>
+        <v>37.4687437</v>
       </c>
       <c r="N62">
-        <v>61.195498</v>
+        <v>60.5812563</v>
       </c>
       <c r="O62">
-        <v>18.3586494</v>
+        <v>18.17437689</v>
       </c>
       <c r="P62">
-        <v>42.8368486</v>
+        <v>42.40687941</v>
       </c>
       <c r="Q62">
-        <v>142.0368486</v>
+        <v>141.60687941</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1806700718806697</v>
+        <v>0.1836221997829983</v>
       </c>
       <c r="T62">
-        <v>1.304296673907649</v>
+        <v>1.33284600698255</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.660461943021236</v>
+        <v>2.616847812807773</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1023139579153694</v>
+        <v>0.1021618870784708</v>
       </c>
       <c r="C63">
-        <v>476.2462442463519</v>
+        <v>470.2159154979948</v>
       </c>
       <c r="D63">
-        <v>931.2692442463518</v>
+        <v>933.7819154979948</v>
       </c>
       <c r="E63">
-        <v>384.3229999999999</v>
+        <v>392.8659999999999</v>
       </c>
       <c r="F63">
-        <v>521.1229999999999</v>
+        <v>529.6659999999999</v>
       </c>
       <c r="G63">
         <v>66.09999999999999</v>
@@ -6453,28 +6453,28 @@
         <v>98.05</v>
       </c>
       <c r="M63">
-        <v>37.4687437</v>
+        <v>38.0829854</v>
       </c>
       <c r="N63">
-        <v>60.5812563</v>
+        <v>59.9670146</v>
       </c>
       <c r="O63">
-        <v>18.17437689</v>
+        <v>17.99010438</v>
       </c>
       <c r="P63">
-        <v>42.40687941</v>
+        <v>41.97691022</v>
       </c>
       <c r="Q63">
-        <v>141.60687941</v>
+        <v>141.17691022</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1836221997829983</v>
+        <v>0.1867297028380811</v>
       </c>
       <c r="T63">
-        <v>1.33284600698255</v>
+        <v>1.362897936535078</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.616847812807773</v>
+        <v>2.57464059002055</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1021618870784708</v>
+        <v>0.1020098162415723</v>
       </c>
       <c r="C64">
-        <v>470.2159154979948</v>
+        <v>464.1991823827721</v>
       </c>
       <c r="D64">
-        <v>933.7819154979948</v>
+        <v>936.308182382772</v>
       </c>
       <c r="E64">
-        <v>392.8659999999999</v>
+        <v>401.4089999999999</v>
       </c>
       <c r="F64">
-        <v>529.6659999999999</v>
+        <v>538.2089999999999</v>
       </c>
       <c r="G64">
         <v>66.09999999999999</v>
@@ -6535,28 +6535,28 @@
         <v>98.05</v>
       </c>
       <c r="M64">
-        <v>38.0829854</v>
+        <v>38.6972271</v>
       </c>
       <c r="N64">
-        <v>59.9670146</v>
+        <v>59.3527729</v>
       </c>
       <c r="O64">
-        <v>17.99010438</v>
+        <v>17.80583187</v>
       </c>
       <c r="P64">
-        <v>41.97691022</v>
+        <v>41.54694103</v>
       </c>
       <c r="Q64">
-        <v>141.17691022</v>
+        <v>140.74694103</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1867297028380811</v>
+        <v>0.1900051790312764</v>
       </c>
       <c r="T64">
-        <v>1.362897936535078</v>
+        <v>1.394574294712068</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.57464059002055</v>
+        <v>2.533773279067843</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1020098162415723</v>
+        <v>0.1036049454046737</v>
       </c>
       <c r="C65">
-        <v>464.1991823827721</v>
+        <v>429.8187306403037</v>
       </c>
       <c r="D65">
-        <v>936.308182382772</v>
+        <v>910.4707306403036</v>
       </c>
       <c r="E65">
-        <v>401.4089999999999</v>
+        <v>409.9519999999999</v>
       </c>
       <c r="F65">
-        <v>538.2089999999999</v>
+        <v>546.752</v>
       </c>
       <c r="G65">
         <v>66.09999999999999</v>
@@ -6617,45 +6617,45 @@
         <v>98.05</v>
       </c>
       <c r="M65">
-        <v>38.6972271</v>
+        <v>41.4438016</v>
       </c>
       <c r="N65">
-        <v>59.3527729</v>
+        <v>56.6061984</v>
       </c>
       <c r="O65">
-        <v>17.80583187</v>
+        <v>16.98185952</v>
       </c>
       <c r="P65">
-        <v>41.54694103</v>
+        <v>39.62433888</v>
       </c>
       <c r="Q65">
-        <v>140.74694103</v>
+        <v>138.82433888</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1900051790312764</v>
+        <v>0.1934626261240937</v>
       </c>
       <c r="T65">
-        <v>1.394574294712068</v>
+        <v>1.428010450565556</v>
       </c>
       <c r="U65">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
         <v>0.3</v>
       </c>
       <c r="W65">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.533773279067843</v>
+        <v>2.365854391118405</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1036049454046737</v>
+        <v>0.1034801745677752</v>
       </c>
       <c r="C66">
-        <v>429.8187306403037</v>
+        <v>423.2452148848448</v>
       </c>
       <c r="D66">
-        <v>910.4707306403036</v>
+        <v>912.4402148848447</v>
       </c>
       <c r="E66">
-        <v>409.9519999999999</v>
+        <v>418.4949999999999</v>
       </c>
       <c r="F66">
-        <v>546.752</v>
+        <v>555.295</v>
       </c>
       <c r="G66">
         <v>66.09999999999999</v>
@@ -6699,28 +6699,28 @@
         <v>98.05</v>
       </c>
       <c r="M66">
-        <v>41.4438016</v>
+        <v>42.091361</v>
       </c>
       <c r="N66">
-        <v>56.6061984</v>
+        <v>55.958639</v>
       </c>
       <c r="O66">
-        <v>16.98185952</v>
+        <v>16.7875917</v>
       </c>
       <c r="P66">
-        <v>39.62433888</v>
+        <v>39.1710473</v>
       </c>
       <c r="Q66">
-        <v>138.82433888</v>
+        <v>138.3710473</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1934626261240937</v>
+        <v>0.1971176416222148</v>
       </c>
       <c r="T66">
-        <v>1.428010450565556</v>
+        <v>1.463357243896386</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.365854391118405</v>
+        <v>2.329456631255045</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1034801745677752</v>
+        <v>0.1033554037308766</v>
       </c>
       <c r="C67">
-        <v>423.2452148848448</v>
+        <v>416.6802381780773</v>
       </c>
       <c r="D67">
-        <v>912.4402148848447</v>
+        <v>914.4182381780772</v>
       </c>
       <c r="E67">
-        <v>418.4949999999999</v>
+        <v>427.038</v>
       </c>
       <c r="F67">
-        <v>555.295</v>
+        <v>563.838</v>
       </c>
       <c r="G67">
         <v>66.09999999999999</v>
@@ -6781,28 +6781,28 @@
         <v>98.05</v>
       </c>
       <c r="M67">
-        <v>42.091361</v>
+        <v>42.7389204</v>
       </c>
       <c r="N67">
-        <v>55.958639</v>
+        <v>55.3110796</v>
       </c>
       <c r="O67">
-        <v>16.7875917</v>
+        <v>16.59332388</v>
       </c>
       <c r="P67">
-        <v>39.1710473</v>
+        <v>38.71775572</v>
       </c>
       <c r="Q67">
-        <v>138.3710473</v>
+        <v>137.91775572</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1971176416222148</v>
+        <v>0.2009876580319902</v>
       </c>
       <c r="T67">
-        <v>1.463357243896386</v>
+        <v>1.500783260364325</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.329456631255045</v>
+        <v>2.294161833811788</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1033554037308766</v>
+        <v>0.1032306328939781</v>
       </c>
       <c r="C68">
-        <v>416.6802381780773</v>
+        <v>410.1238561744937</v>
       </c>
       <c r="D68">
-        <v>914.4182381780772</v>
+        <v>916.4048561744936</v>
       </c>
       <c r="E68">
-        <v>427.038</v>
+        <v>435.581</v>
       </c>
       <c r="F68">
-        <v>563.838</v>
+        <v>572.381</v>
       </c>
       <c r="G68">
         <v>66.09999999999999</v>
@@ -6863,28 +6863,28 @@
         <v>98.05</v>
       </c>
       <c r="M68">
-        <v>42.7389204</v>
+        <v>43.3864798</v>
       </c>
       <c r="N68">
-        <v>55.3110796</v>
+        <v>54.66352019999999</v>
       </c>
       <c r="O68">
-        <v>16.59332388</v>
+        <v>16.39905606</v>
       </c>
       <c r="P68">
-        <v>38.71775572</v>
+        <v>38.26446414</v>
       </c>
       <c r="Q68">
-        <v>137.91775572</v>
+        <v>137.46446414</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2009876580319902</v>
+        <v>0.2050922208908428</v>
       </c>
       <c r="T68">
-        <v>1.500783260364325</v>
+        <v>1.540477520254562</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.294161833811788</v>
+        <v>2.259920612411611</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1032306328939781</v>
+        <v>0.1031058620570796</v>
       </c>
       <c r="C69">
-        <v>410.1238561744937</v>
+        <v>403.5761250132884</v>
       </c>
       <c r="D69">
-        <v>916.4048561744936</v>
+        <v>918.4001250132884</v>
       </c>
       <c r="E69">
-        <v>435.581</v>
+        <v>444.124</v>
       </c>
       <c r="F69">
-        <v>572.381</v>
+        <v>580.924</v>
       </c>
       <c r="G69">
         <v>66.09999999999999</v>
@@ -6945,28 +6945,28 @@
         <v>98.05</v>
       </c>
       <c r="M69">
-        <v>43.3864798</v>
+        <v>44.0340392</v>
       </c>
       <c r="N69">
-        <v>54.66352019999999</v>
+        <v>54.01596079999999</v>
       </c>
       <c r="O69">
-        <v>16.39905606</v>
+        <v>16.20478824</v>
       </c>
       <c r="P69">
-        <v>38.26446414</v>
+        <v>37.81117256</v>
       </c>
       <c r="Q69">
-        <v>137.46446414</v>
+        <v>137.01117256</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2050922208908428</v>
+        <v>0.2094533189283737</v>
       </c>
       <c r="T69">
-        <v>1.540477520254562</v>
+        <v>1.58265267138794</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.259920612411611</v>
+        <v>2.226686485758499</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1031058620570796</v>
+        <v>0.102981091220181</v>
       </c>
       <c r="C70">
-        <v>403.5761250132884</v>
+        <v>397.0371013236462</v>
       </c>
       <c r="D70">
-        <v>918.4001250132884</v>
+        <v>920.4041013236462</v>
       </c>
       <c r="E70">
-        <v>444.124</v>
+        <v>452.667</v>
       </c>
       <c r="F70">
-        <v>580.924</v>
+        <v>589.467</v>
       </c>
       <c r="G70">
         <v>66.09999999999999</v>
@@ -7027,28 +7027,28 @@
         <v>98.05</v>
       </c>
       <c r="M70">
-        <v>44.0340392</v>
+        <v>44.6815986</v>
       </c>
       <c r="N70">
-        <v>54.01596079999999</v>
+        <v>53.3684014</v>
       </c>
       <c r="O70">
-        <v>16.20478824</v>
+        <v>16.01052042</v>
       </c>
       <c r="P70">
-        <v>37.81117256</v>
+        <v>37.35788098</v>
       </c>
       <c r="Q70">
-        <v>137.01117256</v>
+        <v>136.55788098</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2094533189283737</v>
+        <v>0.2140957781296163</v>
       </c>
       <c r="T70">
-        <v>1.58265267138794</v>
+        <v>1.627548800013793</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.226686485758499</v>
+        <v>2.194415667124318</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.102981091220181</v>
+        <v>0.1028563203832825</v>
       </c>
       <c r="C71">
-        <v>397.0371013236462</v>
+        <v>390.5068422300969</v>
       </c>
       <c r="D71">
-        <v>920.4041013236462</v>
+        <v>922.4168422300969</v>
       </c>
       <c r="E71">
-        <v>452.667</v>
+        <v>461.21</v>
       </c>
       <c r="F71">
-        <v>589.467</v>
+        <v>598.01</v>
       </c>
       <c r="G71">
         <v>66.09999999999999</v>
@@ -7109,28 +7109,28 @@
         <v>98.05</v>
       </c>
       <c r="M71">
-        <v>44.6815986</v>
+        <v>45.329158</v>
       </c>
       <c r="N71">
-        <v>53.3684014</v>
+        <v>52.720842</v>
       </c>
       <c r="O71">
-        <v>16.01052042</v>
+        <v>15.8162526</v>
       </c>
       <c r="P71">
-        <v>37.35788098</v>
+        <v>36.9045894</v>
       </c>
       <c r="Q71">
-        <v>136.55788098</v>
+        <v>136.1045894</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2140957781296163</v>
+        <v>0.2190477346109417</v>
       </c>
       <c r="T71">
-        <v>1.627548800013793</v>
+        <v>1.67543800388137</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.194415667124318</v>
+        <v>2.163066871879685</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1028563203832825</v>
+        <v>0.102731549546384</v>
       </c>
       <c r="C72">
-        <v>390.5068422300969</v>
+        <v>383.9854053579471</v>
       </c>
       <c r="D72">
-        <v>922.4168422300969</v>
+        <v>924.4384053579471</v>
       </c>
       <c r="E72">
-        <v>461.21</v>
+        <v>469.753</v>
       </c>
       <c r="F72">
-        <v>598.01</v>
+        <v>606.553</v>
       </c>
       <c r="G72">
         <v>66.09999999999999</v>
@@ -7191,28 +7191,28 @@
         <v>98.05</v>
       </c>
       <c r="M72">
-        <v>45.329158</v>
+        <v>45.97671740000001</v>
       </c>
       <c r="N72">
-        <v>52.720842</v>
+        <v>52.07328259999999</v>
       </c>
       <c r="O72">
-        <v>15.8162526</v>
+        <v>15.62198478</v>
       </c>
       <c r="P72">
-        <v>36.9045894</v>
+        <v>36.45129781999999</v>
       </c>
       <c r="Q72">
-        <v>136.1045894</v>
+        <v>135.65129782</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2190477346109417</v>
+        <v>0.2243412053323585</v>
       </c>
       <c r="T72">
-        <v>1.67543800388137</v>
+        <v>1.726629911463953</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.163066871879685</v>
+        <v>2.13260114128983</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.102731549546384</v>
+        <v>0.1026067787094854</v>
       </c>
       <c r="C73">
-        <v>383.9854053579476</v>
+        <v>377.472848838778</v>
       </c>
       <c r="D73">
-        <v>924.4384053579474</v>
+        <v>926.4688488387778</v>
       </c>
       <c r="E73">
-        <v>469.7529999999999</v>
+        <v>478.2959999999999</v>
       </c>
       <c r="F73">
-        <v>606.5529999999999</v>
+        <v>615.0959999999999</v>
       </c>
       <c r="G73">
         <v>66.09999999999999</v>
@@ -7273,28 +7273,28 @@
         <v>98.05</v>
       </c>
       <c r="M73">
-        <v>45.9767174</v>
+        <v>46.6242768</v>
       </c>
       <c r="N73">
-        <v>52.0732826</v>
+        <v>51.4257232</v>
       </c>
       <c r="O73">
-        <v>15.62198478</v>
+        <v>15.42771696</v>
       </c>
       <c r="P73">
-        <v>36.45129782</v>
+        <v>35.99800624</v>
       </c>
       <c r="Q73">
-        <v>135.65129782</v>
+        <v>135.19800624</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2243412053323584</v>
+        <v>0.230012781105305</v>
       </c>
       <c r="T73">
-        <v>1.726629911463952</v>
+        <v>1.781478383873862</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.13260114128983</v>
+        <v>2.102981680994138</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1026067787094854</v>
+        <v>0.1024820078725869</v>
       </c>
       <c r="C74">
-        <v>377.472848838778</v>
+        <v>370.9692313160167</v>
       </c>
       <c r="D74">
-        <v>926.4688488387778</v>
+        <v>928.5082313160166</v>
       </c>
       <c r="E74">
-        <v>478.2959999999999</v>
+        <v>486.8389999999999</v>
       </c>
       <c r="F74">
-        <v>615.0959999999999</v>
+        <v>623.6389999999999</v>
       </c>
       <c r="G74">
         <v>66.09999999999999</v>
@@ -7355,28 +7355,28 @@
         <v>98.05</v>
       </c>
       <c r="M74">
-        <v>46.6242768</v>
+        <v>47.2718362</v>
       </c>
       <c r="N74">
-        <v>51.4257232</v>
+        <v>50.7781638</v>
       </c>
       <c r="O74">
-        <v>15.42771696</v>
+        <v>15.23344914</v>
       </c>
       <c r="P74">
-        <v>35.99800624</v>
+        <v>35.54471466</v>
       </c>
       <c r="Q74">
-        <v>135.19800624</v>
+        <v>134.74471466</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.230012781105305</v>
+        <v>0.2361044736021736</v>
       </c>
       <c r="T74">
-        <v>1.781478383873862</v>
+        <v>1.840389706091913</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.102981680994138</v>
+        <v>2.074173712761342</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1024820078725869</v>
+        <v>0.1023572370356883</v>
       </c>
       <c r="C75">
-        <v>370.9692313160167</v>
+        <v>364.4746119505829</v>
       </c>
       <c r="D75">
-        <v>928.5082313160166</v>
+        <v>930.5566119505828</v>
       </c>
       <c r="E75">
-        <v>486.8389999999999</v>
+        <v>495.3819999999999</v>
       </c>
       <c r="F75">
-        <v>623.6389999999999</v>
+        <v>632.1819999999999</v>
       </c>
       <c r="G75">
         <v>66.09999999999999</v>
@@ -7437,28 +7437,28 @@
         <v>98.05</v>
       </c>
       <c r="M75">
-        <v>47.2718362</v>
+        <v>47.91939559999999</v>
       </c>
       <c r="N75">
-        <v>50.7781638</v>
+        <v>50.1306044</v>
       </c>
       <c r="O75">
-        <v>15.23344914</v>
+        <v>15.03918132</v>
       </c>
       <c r="P75">
-        <v>35.54471466</v>
+        <v>35.09142308</v>
       </c>
       <c r="Q75">
-        <v>134.74471466</v>
+        <v>134.29142308</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2361044736021736</v>
+        <v>0.2426647578295705</v>
       </c>
       <c r="T75">
-        <v>1.840389706091913</v>
+        <v>1.903832668480583</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.074173712761342</v>
+        <v>2.046144338264567</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1023572370356883</v>
+        <v>0.1022324661987898</v>
       </c>
       <c r="C76">
-        <v>364.4746119505829</v>
+        <v>357.9890504266111</v>
       </c>
       <c r="D76">
-        <v>930.5566119505828</v>
+        <v>932.614050426611</v>
       </c>
       <c r="E76">
-        <v>495.3819999999999</v>
+        <v>503.9249999999999</v>
       </c>
       <c r="F76">
-        <v>632.1819999999999</v>
+        <v>640.7249999999999</v>
       </c>
       <c r="G76">
         <v>66.09999999999999</v>
@@ -7519,28 +7519,28 @@
         <v>98.05</v>
       </c>
       <c r="M76">
-        <v>47.91939559999999</v>
+        <v>48.566955</v>
       </c>
       <c r="N76">
-        <v>50.1306044</v>
+        <v>49.483045</v>
       </c>
       <c r="O76">
-        <v>15.03918132</v>
+        <v>14.8449135</v>
       </c>
       <c r="P76">
-        <v>35.09142308</v>
+        <v>34.6381315</v>
       </c>
       <c r="Q76">
-        <v>134.29142308</v>
+        <v>133.8381315</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2426647578295705</v>
+        <v>0.2497498647951591</v>
       </c>
       <c r="T76">
-        <v>1.903832668480583</v>
+        <v>1.972351067860347</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.046144338264567</v>
+        <v>2.018862413754372</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1022324661987898</v>
+        <v>0.1096620953618913</v>
       </c>
       <c r="C77">
-        <v>357.9890504266111</v>
+        <v>240.947002474882</v>
       </c>
       <c r="D77">
-        <v>932.614050426611</v>
+        <v>824.115002474882</v>
       </c>
       <c r="E77">
-        <v>503.9249999999999</v>
+        <v>512.4680000000001</v>
       </c>
       <c r="F77">
-        <v>640.7249999999999</v>
+        <v>649.268</v>
       </c>
       <c r="G77">
         <v>66.09999999999999</v>
@@ -7601,45 +7601,45 @@
         <v>98.05</v>
       </c>
       <c r="M77">
-        <v>48.566955</v>
+        <v>58.43412</v>
       </c>
       <c r="N77">
-        <v>49.483045</v>
+        <v>39.61588</v>
       </c>
       <c r="O77">
-        <v>14.8449135</v>
+        <v>11.884764</v>
       </c>
       <c r="P77">
-        <v>34.6381315</v>
+        <v>27.731116</v>
       </c>
       <c r="Q77">
-        <v>133.8381315</v>
+        <v>126.931116</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2497498647951591</v>
+        <v>0.2574253973412136</v>
       </c>
       <c r="T77">
-        <v>1.972351067860347</v>
+        <v>2.046579333855091</v>
       </c>
       <c r="U77">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V77">
         <v>0.3</v>
       </c>
       <c r="W77">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.018862413754372</v>
+        <v>1.677958014940586</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1096620953618913</v>
+        <v>0.1096367245249927</v>
       </c>
       <c r="C78">
-        <v>240.947002474882</v>
+        <v>232.7315331787051</v>
       </c>
       <c r="D78">
-        <v>824.115002474882</v>
+        <v>824.4425331787052</v>
       </c>
       <c r="E78">
-        <v>512.4680000000001</v>
+        <v>521.011</v>
       </c>
       <c r="F78">
-        <v>649.268</v>
+        <v>657.811</v>
       </c>
       <c r="G78">
         <v>66.09999999999999</v>
@@ -7683,28 +7683,28 @@
         <v>98.05</v>
       </c>
       <c r="M78">
-        <v>58.43412</v>
+        <v>59.20299</v>
       </c>
       <c r="N78">
-        <v>39.61588</v>
+        <v>38.84701</v>
       </c>
       <c r="O78">
-        <v>11.884764</v>
+        <v>11.654103</v>
       </c>
       <c r="P78">
-        <v>27.731116</v>
+        <v>27.192907</v>
       </c>
       <c r="Q78">
-        <v>126.931116</v>
+        <v>126.392907</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2574253973412136</v>
+        <v>0.2657683674999683</v>
       </c>
       <c r="T78">
-        <v>2.046579333855091</v>
+        <v>2.127262231675465</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.677958014940586</v>
+        <v>1.65616635240889</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1096367245249927</v>
+        <v>0.1096113536880942</v>
       </c>
       <c r="C79">
-        <v>232.7315331787051</v>
+        <v>224.5163243292226</v>
       </c>
       <c r="D79">
-        <v>824.4425331787052</v>
+        <v>824.7703243292226</v>
       </c>
       <c r="E79">
-        <v>521.011</v>
+        <v>529.5540000000001</v>
       </c>
       <c r="F79">
-        <v>657.811</v>
+        <v>666.354</v>
       </c>
       <c r="G79">
         <v>66.09999999999999</v>
@@ -7765,28 +7765,28 @@
         <v>98.05</v>
       </c>
       <c r="M79">
-        <v>59.20299</v>
+        <v>59.97186</v>
       </c>
       <c r="N79">
-        <v>38.84701</v>
+        <v>38.07814</v>
       </c>
       <c r="O79">
-        <v>11.654103</v>
+        <v>11.423442</v>
       </c>
       <c r="P79">
-        <v>27.192907</v>
+        <v>26.654698</v>
       </c>
       <c r="Q79">
-        <v>126.392907</v>
+        <v>125.854698</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2657683674999683</v>
+        <v>0.2748697894913371</v>
       </c>
       <c r="T79">
-        <v>2.127262231675465</v>
+        <v>2.215279938388601</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.65616635240889</v>
+        <v>1.63493345045493</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1096113536880942</v>
+        <v>0.1095859828511956</v>
       </c>
       <c r="C80">
-        <v>224.5163243292226</v>
+        <v>216.3013762372121</v>
       </c>
       <c r="D80">
-        <v>824.7703243292226</v>
+        <v>825.0983762372122</v>
       </c>
       <c r="E80">
-        <v>529.5540000000001</v>
+        <v>538.097</v>
       </c>
       <c r="F80">
-        <v>666.354</v>
+        <v>674.897</v>
       </c>
       <c r="G80">
         <v>66.09999999999999</v>
@@ -7847,28 +7847,28 @@
         <v>98.05</v>
       </c>
       <c r="M80">
-        <v>59.97186</v>
+        <v>60.74073</v>
       </c>
       <c r="N80">
-        <v>38.07814</v>
+        <v>37.30927</v>
       </c>
       <c r="O80">
-        <v>11.423442</v>
+        <v>11.192781</v>
       </c>
       <c r="P80">
-        <v>26.654698</v>
+        <v>26.116489</v>
       </c>
       <c r="Q80">
-        <v>125.854698</v>
+        <v>125.316489</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2748697894913371</v>
+        <v>0.284838013577122</v>
       </c>
       <c r="T80">
-        <v>2.215279938388601</v>
+        <v>2.311680283836321</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.63493345045493</v>
+        <v>1.614238090322589</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1095859828511956</v>
+        <v>0.1095606120142971</v>
       </c>
       <c r="C81">
-        <v>216.3013762372121</v>
+        <v>208.0866892139456</v>
       </c>
       <c r="D81">
-        <v>825.0983762372122</v>
+        <v>825.4266892139457</v>
       </c>
       <c r="E81">
-        <v>538.097</v>
+        <v>546.6400000000001</v>
       </c>
       <c r="F81">
-        <v>674.897</v>
+        <v>683.4400000000001</v>
       </c>
       <c r="G81">
         <v>66.09999999999999</v>
@@ -7929,28 +7929,28 @@
         <v>98.05</v>
       </c>
       <c r="M81">
-        <v>60.74073</v>
+        <v>61.50960000000001</v>
       </c>
       <c r="N81">
-        <v>37.30927</v>
+        <v>36.54039999999999</v>
       </c>
       <c r="O81">
-        <v>11.192781</v>
+        <v>10.96212</v>
       </c>
       <c r="P81">
-        <v>26.116489</v>
+        <v>25.57827999999999</v>
       </c>
       <c r="Q81">
-        <v>125.316489</v>
+        <v>124.77828</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.284838013577122</v>
+        <v>0.2958030600714854</v>
       </c>
       <c r="T81">
-        <v>2.311680283836321</v>
+        <v>2.417720663828812</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.614238090322589</v>
+        <v>1.594060114193557</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1095606120142971</v>
+        <v>0.1095352411773985</v>
       </c>
       <c r="C82">
-        <v>208.0866892139456</v>
+        <v>199.8722635711908</v>
       </c>
       <c r="D82">
-        <v>825.4266892139457</v>
+        <v>825.7552635711909</v>
       </c>
       <c r="E82">
-        <v>546.6400000000001</v>
+        <v>555.183</v>
       </c>
       <c r="F82">
-        <v>683.4400000000001</v>
+        <v>691.9830000000001</v>
       </c>
       <c r="G82">
         <v>66.09999999999999</v>
@@ -8011,28 +8011,28 @@
         <v>98.05</v>
       </c>
       <c r="M82">
-        <v>61.50960000000001</v>
+        <v>62.27847000000001</v>
       </c>
       <c r="N82">
-        <v>36.54039999999999</v>
+        <v>35.77152999999999</v>
       </c>
       <c r="O82">
-        <v>10.96212</v>
+        <v>10.731459</v>
       </c>
       <c r="P82">
-        <v>25.57827999999999</v>
+        <v>25.04007099999999</v>
       </c>
       <c r="Q82">
-        <v>124.77828</v>
+        <v>124.240071</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2958030600714854</v>
+        <v>0.3079223219863081</v>
       </c>
       <c r="T82">
-        <v>2.417720663828812</v>
+        <v>2.534923189083672</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.594060114193557</v>
+        <v>1.57438035969734</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1095352411773985</v>
+        <v>0.1095098703405</v>
       </c>
       <c r="C83">
-        <v>199.8722635711908</v>
+        <v>191.6580996212128</v>
       </c>
       <c r="D83">
-        <v>825.7552635711909</v>
+        <v>826.0840996212129</v>
       </c>
       <c r="E83">
-        <v>555.183</v>
+        <v>563.7260000000001</v>
       </c>
       <c r="F83">
-        <v>691.9830000000001</v>
+        <v>700.5260000000001</v>
       </c>
       <c r="G83">
         <v>66.09999999999999</v>
@@ -8093,28 +8093,28 @@
         <v>98.05</v>
       </c>
       <c r="M83">
-        <v>62.27847000000001</v>
+        <v>63.04734000000001</v>
       </c>
       <c r="N83">
-        <v>35.77152999999999</v>
+        <v>35.00265999999999</v>
       </c>
       <c r="O83">
-        <v>10.731459</v>
+        <v>10.500798</v>
       </c>
       <c r="P83">
-        <v>25.04007099999999</v>
+        <v>24.501862</v>
       </c>
       <c r="Q83">
-        <v>124.240071</v>
+        <v>123.701862</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3079223219863081</v>
+        <v>0.3213881685583334</v>
       </c>
       <c r="T83">
-        <v>2.534923189083672</v>
+        <v>2.665148217144627</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.57438035969734</v>
+        <v>1.555180599213226</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1095098703405</v>
+        <v>0.1094844995036015</v>
       </c>
       <c r="C84">
-        <v>191.6580996212128</v>
+        <v>183.4441976767733</v>
       </c>
       <c r="D84">
-        <v>826.0840996212129</v>
+        <v>826.4131976767734</v>
       </c>
       <c r="E84">
-        <v>563.7260000000001</v>
+        <v>572.269</v>
       </c>
       <c r="F84">
-        <v>700.5260000000001</v>
+        <v>709.0690000000001</v>
       </c>
       <c r="G84">
         <v>66.09999999999999</v>
@@ -8175,28 +8175,28 @@
         <v>98.05</v>
       </c>
       <c r="M84">
-        <v>63.04734000000001</v>
+        <v>63.81621000000001</v>
       </c>
       <c r="N84">
-        <v>35.00265999999999</v>
+        <v>34.23378999999999</v>
       </c>
       <c r="O84">
-        <v>10.500798</v>
+        <v>10.270137</v>
       </c>
       <c r="P84">
-        <v>24.501862</v>
+        <v>23.96365299999999</v>
       </c>
       <c r="Q84">
-        <v>123.701862</v>
+        <v>123.163653</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3213881685583334</v>
+        <v>0.3364382323741263</v>
       </c>
       <c r="T84">
-        <v>2.665148217144627</v>
+        <v>2.810693836742165</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.555180599213226</v>
+        <v>1.536443483560054</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1094844995036015</v>
+        <v>0.1094591286667029</v>
       </c>
       <c r="C85">
-        <v>183.4441976767733</v>
+        <v>175.2305580511326</v>
       </c>
       <c r="D85">
-        <v>826.4131976767734</v>
+        <v>826.7425580511326</v>
       </c>
       <c r="E85">
-        <v>572.269</v>
+        <v>580.8120000000001</v>
       </c>
       <c r="F85">
-        <v>709.0690000000001</v>
+        <v>717.6120000000001</v>
       </c>
       <c r="G85">
         <v>66.09999999999999</v>
@@ -8257,28 +8257,28 @@
         <v>98.05</v>
       </c>
       <c r="M85">
-        <v>63.81621000000001</v>
+        <v>64.58508</v>
       </c>
       <c r="N85">
-        <v>34.23378999999999</v>
+        <v>33.46491999999999</v>
       </c>
       <c r="O85">
-        <v>10.270137</v>
+        <v>10.039476</v>
       </c>
       <c r="P85">
-        <v>23.96365299999999</v>
+        <v>23.425444</v>
       </c>
       <c r="Q85">
-        <v>123.163653</v>
+        <v>122.625444</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3364382323741263</v>
+        <v>0.3533695541668934</v>
       </c>
       <c r="T85">
-        <v>2.810693836742165</v>
+        <v>2.974432658789396</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.536443483560054</v>
+        <v>1.518152489708149</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1094591286667029</v>
+        <v>0.1094337578298044</v>
       </c>
       <c r="C86">
-        <v>175.2305580511327</v>
+        <v>167.0171810580514</v>
       </c>
       <c r="D86">
-        <v>826.7425580511326</v>
+        <v>827.0721810580513</v>
       </c>
       <c r="E86">
-        <v>580.8119999999999</v>
+        <v>589.355</v>
       </c>
       <c r="F86">
-        <v>717.612</v>
+        <v>726.155</v>
       </c>
       <c r="G86">
         <v>66.09999999999999</v>
@@ -8339,28 +8339,28 @@
         <v>98.05</v>
       </c>
       <c r="M86">
-        <v>64.58507999999999</v>
+        <v>65.35395</v>
       </c>
       <c r="N86">
-        <v>33.46492000000001</v>
+        <v>32.69605</v>
       </c>
       <c r="O86">
-        <v>10.039476</v>
+        <v>9.808814999999999</v>
       </c>
       <c r="P86">
-        <v>23.42544400000001</v>
+        <v>22.887235</v>
       </c>
       <c r="Q86">
-        <v>122.625444</v>
+        <v>122.087235</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3533695541668931</v>
+        <v>0.3725583855320291</v>
       </c>
       <c r="T86">
-        <v>2.974432658789393</v>
+        <v>3.160003323776254</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.51815248970815</v>
+        <v>1.500291872182171</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1094337578298044</v>
+        <v>0.1485875788143424</v>
       </c>
       <c r="C87">
-        <v>167.0171810580514</v>
+        <v>-156.5739647585694</v>
       </c>
       <c r="D87">
-        <v>827.0721810580513</v>
+        <v>512.0240352414305</v>
       </c>
       <c r="E87">
-        <v>589.355</v>
+        <v>597.8979999999999</v>
       </c>
       <c r="F87">
-        <v>726.155</v>
+        <v>734.698</v>
       </c>
       <c r="G87">
         <v>66.09999999999999</v>
@@ -8421,45 +8421,45 @@
         <v>98.05</v>
       </c>
       <c r="M87">
-        <v>65.35395</v>
+        <v>107.8536664</v>
       </c>
       <c r="N87">
-        <v>32.69605</v>
+        <v>-9.803666400000012</v>
       </c>
       <c r="O87">
-        <v>9.808814999999999</v>
+        <v>-2.941099920000003</v>
       </c>
       <c r="P87">
-        <v>22.887235</v>
+        <v>-6.862566480000009</v>
       </c>
       <c r="Q87">
-        <v>122.087235</v>
+        <v>92.33743351999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3725583855320291</v>
+        <v>0.4055091234351655</v>
       </c>
       <c r="T87">
-        <v>3.160003323776254</v>
+        <v>3.47866214296847</v>
       </c>
       <c r="U87">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.3</v>
+        <v>0.2727306449732338</v>
       </c>
       <c r="W87">
-        <v>0.063</v>
+        <v>0.1067631413179293</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y87">
-        <v>1.500291872182171</v>
+        <v>0.9091021499107794</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1485875788143424</v>
+        <v>0.1495975788143424</v>
       </c>
       <c r="C88">
-        <v>-156.5739647585694</v>
+        <v>-170.0992030872575</v>
       </c>
       <c r="D88">
-        <v>512.0240352414305</v>
+        <v>507.0417969127425</v>
       </c>
       <c r="E88">
-        <v>597.8979999999999</v>
+        <v>606.441</v>
       </c>
       <c r="F88">
-        <v>734.698</v>
+        <v>743.241</v>
       </c>
       <c r="G88">
         <v>66.09999999999999</v>
@@ -8503,37 +8503,37 @@
         <v>98.05</v>
       </c>
       <c r="M88">
-        <v>107.8536664</v>
+        <v>109.1077788</v>
       </c>
       <c r="N88">
-        <v>-9.803666400000012</v>
+        <v>-11.05777880000001</v>
       </c>
       <c r="O88">
-        <v>-2.941099920000003</v>
+        <v>-3.317333640000002</v>
       </c>
       <c r="P88">
-        <v>-6.862566480000009</v>
+        <v>-7.740445160000005</v>
       </c>
       <c r="Q88">
-        <v>92.33743351999999</v>
+        <v>91.45955484</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4055091234351655</v>
+        <v>0.4331790560071013</v>
       </c>
       <c r="T88">
-        <v>3.47866214296847</v>
+        <v>3.746251538581429</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2727306449732338</v>
+        <v>0.2695958099735415</v>
       </c>
       <c r="W88">
-        <v>0.1067631413179293</v>
+        <v>0.1072233350958841</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9091021499107794</v>
+        <v>0.898652699911805</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1495975788143424</v>
+        <v>0.1506075788143424</v>
       </c>
       <c r="C89">
-        <v>-170.0992030872575</v>
+        <v>-183.5284166671843</v>
       </c>
       <c r="D89">
-        <v>507.0417969127425</v>
+        <v>502.1555833328158</v>
       </c>
       <c r="E89">
-        <v>606.441</v>
+        <v>614.9839999999999</v>
       </c>
       <c r="F89">
-        <v>743.241</v>
+        <v>751.784</v>
       </c>
       <c r="G89">
         <v>66.09999999999999</v>
@@ -8585,37 +8585,37 @@
         <v>98.05</v>
       </c>
       <c r="M89">
-        <v>109.1077788</v>
+        <v>110.3618912</v>
       </c>
       <c r="N89">
-        <v>-11.05777880000001</v>
+        <v>-12.31189120000001</v>
       </c>
       <c r="O89">
-        <v>-3.317333640000002</v>
+        <v>-3.693567360000001</v>
       </c>
       <c r="P89">
-        <v>-7.740445160000005</v>
+        <v>-8.618323840000004</v>
       </c>
       <c r="Q89">
-        <v>91.45955484</v>
+        <v>90.58167616</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4331790560071013</v>
+        <v>0.465460644007693</v>
       </c>
       <c r="T89">
-        <v>3.746251538581429</v>
+        <v>4.058439166796548</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2695958099735415</v>
+        <v>0.2665322212238421</v>
       </c>
       <c r="W89">
-        <v>0.1072233350958841</v>
+        <v>0.10767306992434</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.898652699911805</v>
+        <v>0.8884407374128072</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1506075788143424</v>
+        <v>0.1516175788143423</v>
       </c>
       <c r="C90">
-        <v>-183.5284166671843</v>
+        <v>-196.8643550886537</v>
       </c>
       <c r="D90">
-        <v>502.1555833328158</v>
+        <v>497.3626449113463</v>
       </c>
       <c r="E90">
-        <v>614.9839999999999</v>
+        <v>623.527</v>
       </c>
       <c r="F90">
-        <v>751.784</v>
+        <v>760.327</v>
       </c>
       <c r="G90">
         <v>66.09999999999999</v>
@@ -8667,37 +8667,37 @@
         <v>98.05</v>
       </c>
       <c r="M90">
-        <v>110.3618912</v>
+        <v>111.6160036</v>
       </c>
       <c r="N90">
-        <v>-12.31189120000001</v>
+        <v>-13.56600360000002</v>
       </c>
       <c r="O90">
-        <v>-3.693567360000001</v>
+        <v>-4.069801080000005</v>
       </c>
       <c r="P90">
-        <v>-8.618323840000004</v>
+        <v>-9.496202520000011</v>
       </c>
       <c r="Q90">
-        <v>90.58167616</v>
+        <v>89.70379747999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.465460644007693</v>
+        <v>0.5036116116447561</v>
       </c>
       <c r="T90">
-        <v>4.058439166796548</v>
+        <v>4.427388181959871</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2665322212238421</v>
+        <v>0.2635374771651472</v>
       </c>
       <c r="W90">
-        <v>0.10767306992434</v>
+        <v>0.1081126983521564</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8884407374128072</v>
+        <v>0.8784582572171575</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1516175788143423</v>
+        <v>0.1526275788143424</v>
       </c>
       <c r="C91">
-        <v>-196.8643550886537</v>
+        <v>-210.1096639581029</v>
       </c>
       <c r="D91">
-        <v>497.3626449113463</v>
+        <v>492.6603360418971</v>
       </c>
       <c r="E91">
-        <v>623.527</v>
+        <v>632.0699999999999</v>
       </c>
       <c r="F91">
-        <v>760.327</v>
+        <v>768.87</v>
       </c>
       <c r="G91">
         <v>66.09999999999999</v>
@@ -8749,37 +8749,37 @@
         <v>98.05</v>
       </c>
       <c r="M91">
-        <v>111.6160036</v>
+        <v>112.870116</v>
       </c>
       <c r="N91">
-        <v>-13.56600360000002</v>
+        <v>-14.82011600000001</v>
       </c>
       <c r="O91">
-        <v>-4.069801080000005</v>
+        <v>-4.446034800000004</v>
       </c>
       <c r="P91">
-        <v>-9.496202520000011</v>
+        <v>-10.37408120000001</v>
       </c>
       <c r="Q91">
-        <v>89.70379747999999</v>
+        <v>88.8259188</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5036116116447561</v>
+        <v>0.5493927728092317</v>
       </c>
       <c r="T91">
-        <v>4.427388181959871</v>
+        <v>4.870127000155859</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2635374771651472</v>
+        <v>0.2606092829744234</v>
       </c>
       <c r="W91">
-        <v>0.1081126983521564</v>
+        <v>0.1085425572593546</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8784582572171575</v>
+        <v>0.8686976099147448</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1526275788143424</v>
+        <v>0.1536375788143423</v>
       </c>
       <c r="C92">
-        <v>-210.1096639581029</v>
+        <v>-223.2668897676324</v>
       </c>
       <c r="D92">
-        <v>492.6603360418971</v>
+        <v>488.0461102323677</v>
       </c>
       <c r="E92">
-        <v>632.0699999999999</v>
+        <v>640.6130000000001</v>
       </c>
       <c r="F92">
-        <v>768.87</v>
+        <v>777.413</v>
       </c>
       <c r="G92">
         <v>66.09999999999999</v>
@@ -8831,37 +8831,37 @@
         <v>98.05</v>
       </c>
       <c r="M92">
-        <v>112.870116</v>
+        <v>114.1242284</v>
       </c>
       <c r="N92">
-        <v>-14.82011600000001</v>
+        <v>-16.07422840000001</v>
       </c>
       <c r="O92">
-        <v>-4.446034800000004</v>
+        <v>-4.822268520000002</v>
       </c>
       <c r="P92">
-        <v>-10.37408120000001</v>
+        <v>-11.25195988000001</v>
       </c>
       <c r="Q92">
-        <v>88.8259188</v>
+        <v>87.94804012</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5493927728092317</v>
+        <v>0.6053475253435908</v>
       </c>
       <c r="T92">
-        <v>4.870127000155859</v>
+        <v>5.411252222395399</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2606092829744234</v>
+        <v>0.2577454446999792</v>
       </c>
       <c r="W92">
-        <v>0.1085425572593546</v>
+        <v>0.1089629687180431</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8686976099147448</v>
+        <v>0.859151482333264</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1536375788143423</v>
+        <v>0.1546475788143424</v>
       </c>
       <c r="C93">
-        <v>-223.2668897676324</v>
+        <v>-236.3384844934321</v>
       </c>
       <c r="D93">
-        <v>488.0461102323677</v>
+        <v>483.5175155065679</v>
       </c>
       <c r="E93">
-        <v>640.6130000000001</v>
+        <v>649.1559999999999</v>
       </c>
       <c r="F93">
-        <v>777.413</v>
+        <v>785.956</v>
       </c>
       <c r="G93">
         <v>66.09999999999999</v>
@@ -8913,37 +8913,37 @@
         <v>98.05</v>
       </c>
       <c r="M93">
-        <v>114.1242284</v>
+        <v>115.3783408</v>
       </c>
       <c r="N93">
-        <v>-16.07422840000001</v>
+        <v>-17.32834080000002</v>
       </c>
       <c r="O93">
-        <v>-4.822268520000002</v>
+        <v>-5.198502240000006</v>
       </c>
       <c r="P93">
-        <v>-11.25195988000001</v>
+        <v>-12.12983856000001</v>
       </c>
       <c r="Q93">
-        <v>87.94804012</v>
+        <v>87.07016143999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6053475253435908</v>
+        <v>0.6752909660115398</v>
       </c>
       <c r="T93">
-        <v>5.411252222395399</v>
+        <v>6.087658750194825</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2577454446999792</v>
+        <v>0.2549438637793273</v>
       </c>
       <c r="W93">
-        <v>0.1089629687180431</v>
+        <v>0.1093742407971948</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.859151482333264</v>
+        <v>0.8498128792644242</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1546475788143424</v>
+        <v>0.1556575788143423</v>
       </c>
       <c r="C94">
-        <v>-236.3384844934321</v>
+        <v>-249.3268099405451</v>
       </c>
       <c r="D94">
-        <v>483.5175155065679</v>
+        <v>479.0721900594549</v>
       </c>
       <c r="E94">
-        <v>649.1559999999999</v>
+        <v>657.6990000000001</v>
       </c>
       <c r="F94">
-        <v>785.956</v>
+        <v>794.499</v>
       </c>
       <c r="G94">
         <v>66.09999999999999</v>
@@ -8995,37 +8995,37 @@
         <v>98.05</v>
       </c>
       <c r="M94">
-        <v>115.3783408</v>
+        <v>116.6324532</v>
       </c>
       <c r="N94">
-        <v>-17.32834080000002</v>
+        <v>-18.58245320000002</v>
       </c>
       <c r="O94">
-        <v>-5.198502240000006</v>
+        <v>-5.574735960000005</v>
       </c>
       <c r="P94">
-        <v>-12.12983856000001</v>
+        <v>-13.00771724000001</v>
       </c>
       <c r="Q94">
-        <v>87.07016143999999</v>
+        <v>86.19228275999998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6752909660115398</v>
+        <v>0.7652182468703314</v>
       </c>
       <c r="T94">
-        <v>6.087658750194825</v>
+        <v>6.957324285936944</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2549438637793273</v>
+        <v>0.2522025319107323</v>
       </c>
       <c r="W94">
-        <v>0.1093742407971948</v>
+        <v>0.1097766683155045</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8498128792644242</v>
+        <v>0.8406751063691078</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1556575788143423</v>
+        <v>0.1566675788143423</v>
       </c>
       <c r="C95">
-        <v>-249.3268099405451</v>
+        <v>-262.2341418501499</v>
       </c>
       <c r="D95">
-        <v>479.0721900594549</v>
+        <v>474.7078581498502</v>
       </c>
       <c r="E95">
-        <v>657.6990000000001</v>
+        <v>666.242</v>
       </c>
       <c r="F95">
-        <v>794.499</v>
+        <v>803.042</v>
       </c>
       <c r="G95">
         <v>66.09999999999999</v>
@@ -9077,37 +9077,37 @@
         <v>98.05</v>
       </c>
       <c r="M95">
-        <v>116.6324532</v>
+        <v>117.8865656</v>
       </c>
       <c r="N95">
-        <v>-18.58245320000002</v>
+        <v>-19.83656560000001</v>
       </c>
       <c r="O95">
-        <v>-5.574735960000005</v>
+        <v>-5.950969680000004</v>
       </c>
       <c r="P95">
-        <v>-13.00771724000001</v>
+        <v>-13.88559592000001</v>
       </c>
       <c r="Q95">
-        <v>86.19228275999998</v>
+        <v>85.31440407999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7652182468703314</v>
+        <v>0.8851212880153868</v>
       </c>
       <c r="T95">
-        <v>6.957324285936944</v>
+        <v>8.116878333593103</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2522025319107323</v>
+        <v>0.2495195262521075</v>
       </c>
       <c r="W95">
-        <v>0.1097766683155045</v>
+        <v>0.1101705335461906</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8406751063691078</v>
+        <v>0.8317317541736917</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1566675788143423</v>
+        <v>0.1576775788143424</v>
       </c>
       <c r="C96">
-        <v>-262.2341418501499</v>
+        <v>-275.0626737843636</v>
       </c>
       <c r="D96">
-        <v>474.7078581498502</v>
+        <v>470.4223262156365</v>
       </c>
       <c r="E96">
-        <v>666.242</v>
+        <v>674.7850000000001</v>
       </c>
       <c r="F96">
-        <v>803.042</v>
+        <v>811.585</v>
       </c>
       <c r="G96">
         <v>66.09999999999999</v>
@@ -9159,37 +9159,37 @@
         <v>98.05</v>
       </c>
       <c r="M96">
-        <v>117.8865656</v>
+        <v>119.140678</v>
       </c>
       <c r="N96">
-        <v>-19.83656560000001</v>
+        <v>-21.09067800000003</v>
       </c>
       <c r="O96">
-        <v>-5.950969680000004</v>
+        <v>-6.327203400000007</v>
       </c>
       <c r="P96">
-        <v>-13.88559592000001</v>
+        <v>-14.76347460000002</v>
       </c>
       <c r="Q96">
-        <v>85.31440407999999</v>
+        <v>84.43652539999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8851212880153868</v>
+        <v>1.052985545618465</v>
       </c>
       <c r="T96">
-        <v>8.116878333593103</v>
+        <v>9.740254000311729</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2495195262521075</v>
+        <v>0.2468930049231379</v>
       </c>
       <c r="W96">
-        <v>0.1101705335461906</v>
+        <v>0.1105561068772834</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8317317541736917</v>
+        <v>0.8229766830771266</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1576775788143424</v>
+        <v>0.1586875788143424</v>
       </c>
       <c r="C97">
-        <v>-275.0626737843636</v>
+        <v>-287.8145208025035</v>
       </c>
       <c r="D97">
-        <v>470.4223262156365</v>
+        <v>466.2134791974966</v>
       </c>
       <c r="E97">
-        <v>674.7850000000001</v>
+        <v>683.328</v>
       </c>
       <c r="F97">
-        <v>811.585</v>
+        <v>820.128</v>
       </c>
       <c r="G97">
         <v>66.09999999999999</v>
@@ -9241,37 +9241,37 @@
         <v>98.05</v>
       </c>
       <c r="M97">
-        <v>119.140678</v>
+        <v>120.3947904</v>
       </c>
       <c r="N97">
-        <v>-21.09067800000003</v>
+        <v>-22.34479040000002</v>
       </c>
       <c r="O97">
-        <v>-6.327203400000007</v>
+        <v>-6.703437120000006</v>
       </c>
       <c r="P97">
-        <v>-14.76347460000002</v>
+        <v>-15.64135328000001</v>
       </c>
       <c r="Q97">
-        <v>84.43652539999998</v>
+        <v>83.55864671999998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.052985545618465</v>
+        <v>1.304781932023081</v>
       </c>
       <c r="T97">
-        <v>9.740254000311729</v>
+        <v>12.17531750038967</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2468930049231379</v>
+        <v>0.2443212027885219</v>
       </c>
       <c r="W97">
-        <v>0.1105561068772834</v>
+        <v>0.110933647430645</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8229766830771266</v>
+        <v>0.8144040092950732</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1586875788143424</v>
+        <v>0.1596975788143424</v>
       </c>
       <c r="C98">
-        <v>-287.8145208025034</v>
+        <v>-300.4917229417518</v>
       </c>
       <c r="D98">
-        <v>466.2134791974966</v>
+        <v>462.0792770582481</v>
       </c>
       <c r="E98">
-        <v>683.328</v>
+        <v>691.8709999999999</v>
       </c>
       <c r="F98">
-        <v>820.1279999999999</v>
+        <v>828.6709999999999</v>
       </c>
       <c r="G98">
         <v>66.09999999999999</v>
@@ -9323,37 +9323,37 @@
         <v>98.05</v>
       </c>
       <c r="M98">
-        <v>120.3947904</v>
+        <v>121.6489028</v>
       </c>
       <c r="N98">
-        <v>-22.34479040000001</v>
+        <v>-23.5989028</v>
       </c>
       <c r="O98">
-        <v>-6.703437120000002</v>
+        <v>-7.079670840000001</v>
       </c>
       <c r="P98">
-        <v>-15.64135328000001</v>
+        <v>-16.51923196</v>
       </c>
       <c r="Q98">
-        <v>83.55864672</v>
+        <v>82.68076804</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.304781932023078</v>
+        <v>1.724442576030771</v>
       </c>
       <c r="T98">
-        <v>12.17531750038963</v>
+        <v>16.23375666718618</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2443212027885219</v>
+        <v>0.2418024275020423</v>
       </c>
       <c r="W98">
-        <v>0.110933647430645</v>
+        <v>0.1113034036427002</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8144040092950733</v>
+        <v>0.8060080916734745</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1596975788143424</v>
+        <v>0.2177773501838837</v>
       </c>
       <c r="C99">
-        <v>-300.4917229417518</v>
+        <v>-465.0870096960862</v>
       </c>
       <c r="D99">
-        <v>462.0792770582481</v>
+        <v>306.0269903039137</v>
       </c>
       <c r="E99">
-        <v>691.8709999999999</v>
+        <v>700.414</v>
       </c>
       <c r="F99">
-        <v>828.6709999999999</v>
+        <v>837.2139999999999</v>
       </c>
       <c r="G99">
         <v>66.09999999999999</v>
@@ -9405,45 +9405,45 @@
         <v>98.05</v>
       </c>
       <c r="M99">
-        <v>121.6489028</v>
+        <v>168.1125712</v>
       </c>
       <c r="N99">
-        <v>-23.5989028</v>
+        <v>-70.06257119999999</v>
       </c>
       <c r="O99">
-        <v>-7.079670840000001</v>
+        <v>-21.01877136</v>
       </c>
       <c r="P99">
-        <v>-16.51923196</v>
+        <v>-49.04379983999999</v>
       </c>
       <c r="Q99">
-        <v>82.68076804</v>
+        <v>50.15620016000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.724442576030771</v>
+        <v>2.77125243252322</v>
       </c>
       <c r="T99">
-        <v>16.23375666718618</v>
+        <v>26.35720803781256</v>
       </c>
       <c r="U99">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.2418024275020423</v>
+        <v>0.1749720427808197</v>
       </c>
       <c r="W99">
-        <v>0.1113034036427002</v>
+        <v>0.1656656138096114</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.8060080916734745</v>
+        <v>0.5832401426027324</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2177773501838837</v>
+        <v>0.2193273501838836</v>
       </c>
       <c r="C100">
-        <v>-465.0870096960862</v>
+        <v>-476.3635374913783</v>
       </c>
       <c r="D100">
-        <v>306.0269903039137</v>
+        <v>303.2934625086216</v>
       </c>
       <c r="E100">
-        <v>700.414</v>
+        <v>708.9569999999999</v>
       </c>
       <c r="F100">
-        <v>837.2139999999999</v>
+        <v>845.7569999999999</v>
       </c>
       <c r="G100">
         <v>66.09999999999999</v>
@@ -9487,37 +9487,37 @@
         <v>98.05</v>
       </c>
       <c r="M100">
-        <v>168.1125712</v>
+        <v>169.8280056</v>
       </c>
       <c r="N100">
-        <v>-70.06257119999999</v>
+        <v>-71.77800559999999</v>
       </c>
       <c r="O100">
-        <v>-21.01877136</v>
+        <v>-21.53340167999999</v>
       </c>
       <c r="P100">
-        <v>-49.04379983999999</v>
+        <v>-50.24460391999999</v>
       </c>
       <c r="Q100">
-        <v>50.15620016000001</v>
+        <v>48.95539608000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.77125243252322</v>
+        <v>5.49670486504644</v>
       </c>
       <c r="T100">
-        <v>26.35720803781256</v>
+        <v>52.71441607562512</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1749720427808197</v>
+        <v>0.1732046484092963</v>
       </c>
       <c r="W100">
-        <v>0.1656656138096114</v>
+        <v>0.1660205065994133</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5832401426027324</v>
+        <v>0.5773488280309876</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2193273501838836</v>
-      </c>
-      <c r="C101">
-        <v>-476.3635374913783</v>
-      </c>
-      <c r="D101">
-        <v>303.2934625086216</v>
-      </c>
-      <c r="E101">
-        <v>708.9569999999999</v>
-      </c>
-      <c r="F101">
-        <v>845.7569999999999</v>
-      </c>
-      <c r="G101">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="H101">
-        <v>717.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>197.25</v>
-      </c>
-      <c r="K101">
-        <v>99.2</v>
-      </c>
-      <c r="L101">
-        <v>98.05</v>
-      </c>
-      <c r="M101">
-        <v>169.8280056</v>
-      </c>
-      <c r="N101">
-        <v>-71.77800559999999</v>
-      </c>
-      <c r="O101">
-        <v>-21.53340167999999</v>
-      </c>
-      <c r="P101">
-        <v>-50.24460391999999</v>
-      </c>
-      <c r="Q101">
-        <v>48.95539608000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.49670486504644</v>
-      </c>
-      <c r="T101">
-        <v>52.71441607562512</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1732046484092963</v>
-      </c>
-      <c r="W101">
-        <v>0.1660205065994133</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5773488280309876</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
